--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA37B26-CD98-4162-B502-46CFE049C301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98F9878-5608-48D1-8294-3B3CCB93FAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="612">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -245,9 +245,6 @@
     <t>IMP*Z</t>
   </si>
   <si>
-    <t>IMPDEMZ</t>
-  </si>
-  <si>
     <t>~Currencies</t>
   </si>
   <si>
@@ -1869,6 +1866,15 @@
   </si>
   <si>
     <t>grid node -- way/759521252-765</t>
+  </si>
+  <si>
+    <t>IMPDEMZ,IMPDUCZ</t>
+  </si>
+  <si>
+    <t>invcost</t>
+  </si>
+  <si>
+    <t>IMPDUCZ</t>
   </si>
 </sst>
 </file>
@@ -4259,7 +4265,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -4289,18 +4295,18 @@
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -4323,25 +4329,25 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>576</v>
+      </c>
+      <c r="D5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" t="s">
         <v>577</v>
       </c>
-      <c r="D5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>578</v>
       </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>579</v>
-      </c>
       <c r="I5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -4349,14 +4355,14 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>579</v>
+      </c>
+      <c r="D6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" t="s">
         <v>580</v>
       </c>
-      <c r="D6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" t="s">
-        <v>581</v>
-      </c>
       <c r="F6" t="s">
         <v>25</v>
       </c>
@@ -4364,10 +4370,10 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -4375,14 +4381,14 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" t="s">
         <v>582</v>
       </c>
-      <c r="D7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E7" t="s">
-        <v>583</v>
-      </c>
       <c r="F7" t="s">
         <v>25</v>
       </c>
@@ -4390,10 +4396,10 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -4401,14 +4407,14 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
+        <v>583</v>
+      </c>
+      <c r="D8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" t="s">
         <v>584</v>
       </c>
-      <c r="D8" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" t="s">
-        <v>585</v>
-      </c>
       <c r="F8" t="s">
         <v>25</v>
       </c>
@@ -4416,10 +4422,10 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -4427,14 +4433,14 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
+        <v>585</v>
+      </c>
+      <c r="D9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" t="s">
         <v>586</v>
       </c>
-      <c r="D9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" t="s">
-        <v>587</v>
-      </c>
       <c r="F9" t="s">
         <v>25</v>
       </c>
@@ -4442,10 +4448,10 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -4453,14 +4459,14 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
+        <v>587</v>
+      </c>
+      <c r="D10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" t="s">
         <v>588</v>
       </c>
-      <c r="D10" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" t="s">
-        <v>589</v>
-      </c>
       <c r="F10" t="s">
         <v>25</v>
       </c>
@@ -4468,10 +4474,10 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -4479,14 +4485,14 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
+        <v>589</v>
+      </c>
+      <c r="D11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" t="s">
         <v>590</v>
       </c>
-      <c r="D11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E11" t="s">
-        <v>591</v>
-      </c>
       <c r="F11" t="s">
         <v>25</v>
       </c>
@@ -4494,10 +4500,10 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -4505,14 +4511,14 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
+        <v>591</v>
+      </c>
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" t="s">
         <v>592</v>
       </c>
-      <c r="D12" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" t="s">
-        <v>593</v>
-      </c>
       <c r="F12" t="s">
         <v>25</v>
       </c>
@@ -4520,10 +4526,10 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -4531,14 +4537,14 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" t="s">
         <v>594</v>
       </c>
-      <c r="D13" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" t="s">
-        <v>595</v>
-      </c>
       <c r="F13" t="s">
         <v>25</v>
       </c>
@@ -4546,10 +4552,10 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="2:9">
@@ -4557,14 +4563,14 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
+        <v>595</v>
+      </c>
+      <c r="D14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" t="s">
         <v>596</v>
       </c>
-      <c r="D14" t="s">
-        <v>235</v>
-      </c>
-      <c r="E14" t="s">
-        <v>597</v>
-      </c>
       <c r="F14" t="s">
         <v>25</v>
       </c>
@@ -4572,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -4583,14 +4589,14 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
+        <v>597</v>
+      </c>
+      <c r="D15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" t="s">
         <v>598</v>
       </c>
-      <c r="D15" t="s">
-        <v>235</v>
-      </c>
-      <c r="E15" t="s">
-        <v>599</v>
-      </c>
       <c r="F15" t="s">
         <v>25</v>
       </c>
@@ -4598,10 +4604,10 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -4609,14 +4615,14 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
+        <v>599</v>
+      </c>
+      <c r="D16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" t="s">
         <v>600</v>
       </c>
-      <c r="D16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" t="s">
-        <v>601</v>
-      </c>
       <c r="F16" t="s">
         <v>25</v>
       </c>
@@ -4624,10 +4630,10 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -4635,14 +4641,14 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
+        <v>601</v>
+      </c>
+      <c r="D17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" t="s">
         <v>602</v>
       </c>
-      <c r="D17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E17" t="s">
-        <v>603</v>
-      </c>
       <c r="F17" t="s">
         <v>25</v>
       </c>
@@ -4650,10 +4656,10 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -4661,14 +4667,14 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
+        <v>603</v>
+      </c>
+      <c r="D18" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" t="s">
         <v>604</v>
       </c>
-      <c r="D18" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" t="s">
-        <v>605</v>
-      </c>
       <c r="F18" t="s">
         <v>25</v>
       </c>
@@ -4676,10 +4682,10 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -4687,14 +4693,14 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
+        <v>605</v>
+      </c>
+      <c r="D19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E19" t="s">
         <v>606</v>
       </c>
-      <c r="D19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E19" t="s">
-        <v>607</v>
-      </c>
       <c r="F19" t="s">
         <v>25</v>
       </c>
@@ -4702,10 +4708,10 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -4713,14 +4719,14 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
+        <v>607</v>
+      </c>
+      <c r="D20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E20" t="s">
         <v>608</v>
       </c>
-      <c r="D20" t="s">
-        <v>235</v>
-      </c>
-      <c r="E20" t="s">
-        <v>609</v>
-      </c>
       <c r="F20" t="s">
         <v>25</v>
       </c>
@@ -4728,10 +4734,10 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4799,13 +4805,13 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>11</v>
@@ -4834,14 +4840,14 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
+        <v>236</v>
+      </c>
+      <c r="O5" t="s">
+        <v>234</v>
+      </c>
+      <c r="P5" t="s">
         <v>237</v>
       </c>
-      <c r="O5" t="s">
-        <v>235</v>
-      </c>
-      <c r="P5" t="s">
-        <v>238</v>
-      </c>
       <c r="Q5" t="s">
         <v>25</v>
       </c>
@@ -4849,7 +4855,7 @@
         <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -4857,7 +4863,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -4866,14 +4872,14 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
+        <v>239</v>
+      </c>
+      <c r="O6" t="s">
+        <v>234</v>
+      </c>
+      <c r="P6" t="s">
         <v>240</v>
       </c>
-      <c r="O6" t="s">
-        <v>235</v>
-      </c>
-      <c r="P6" t="s">
-        <v>241</v>
-      </c>
       <c r="Q6" t="s">
         <v>25</v>
       </c>
@@ -4881,7 +4887,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -4889,7 +4895,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -4898,14 +4904,14 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
+        <v>241</v>
+      </c>
+      <c r="O7" t="s">
+        <v>234</v>
+      </c>
+      <c r="P7" t="s">
         <v>242</v>
       </c>
-      <c r="O7" t="s">
-        <v>235</v>
-      </c>
-      <c r="P7" t="s">
-        <v>243</v>
-      </c>
       <c r="Q7" t="s">
         <v>25</v>
       </c>
@@ -4913,7 +4919,7 @@
         <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -4930,14 +4936,14 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" t="s">
+        <v>234</v>
+      </c>
+      <c r="P8" t="s">
         <v>244</v>
       </c>
-      <c r="O8" t="s">
-        <v>235</v>
-      </c>
-      <c r="P8" t="s">
-        <v>245</v>
-      </c>
       <c r="Q8" t="s">
         <v>25</v>
       </c>
@@ -4945,7 +4951,7 @@
         <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="2:19">
@@ -4962,14 +4968,14 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
+        <v>245</v>
+      </c>
+      <c r="O9" t="s">
+        <v>234</v>
+      </c>
+      <c r="P9" t="s">
         <v>246</v>
       </c>
-      <c r="O9" t="s">
-        <v>235</v>
-      </c>
-      <c r="P9" t="s">
-        <v>247</v>
-      </c>
       <c r="Q9" t="s">
         <v>25</v>
       </c>
@@ -4977,7 +4983,7 @@
         <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="2:19">
@@ -4994,14 +5000,14 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
+        <v>247</v>
+      </c>
+      <c r="O10" t="s">
+        <v>234</v>
+      </c>
+      <c r="P10" t="s">
         <v>248</v>
       </c>
-      <c r="O10" t="s">
-        <v>235</v>
-      </c>
-      <c r="P10" t="s">
-        <v>249</v>
-      </c>
       <c r="Q10" t="s">
         <v>25</v>
       </c>
@@ -5009,7 +5015,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="2:19">
@@ -5026,14 +5032,14 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
+        <v>249</v>
+      </c>
+      <c r="O11" t="s">
+        <v>234</v>
+      </c>
+      <c r="P11" t="s">
         <v>250</v>
       </c>
-      <c r="O11" t="s">
-        <v>235</v>
-      </c>
-      <c r="P11" t="s">
-        <v>251</v>
-      </c>
       <c r="Q11" t="s">
         <v>25</v>
       </c>
@@ -5041,7 +5047,7 @@
         <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="2:19">
@@ -5049,7 +5055,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -5058,14 +5064,14 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
+        <v>251</v>
+      </c>
+      <c r="O12" t="s">
+        <v>234</v>
+      </c>
+      <c r="P12" t="s">
         <v>252</v>
       </c>
-      <c r="O12" t="s">
-        <v>235</v>
-      </c>
-      <c r="P12" t="s">
-        <v>253</v>
-      </c>
       <c r="Q12" t="s">
         <v>25</v>
       </c>
@@ -5073,7 +5079,7 @@
         <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="2:19">
@@ -5090,14 +5096,14 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
+        <v>253</v>
+      </c>
+      <c r="O13" t="s">
+        <v>234</v>
+      </c>
+      <c r="P13" t="s">
         <v>254</v>
       </c>
-      <c r="O13" t="s">
-        <v>235</v>
-      </c>
-      <c r="P13" t="s">
-        <v>255</v>
-      </c>
       <c r="Q13" t="s">
         <v>25</v>
       </c>
@@ -5105,7 +5111,7 @@
         <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="2:19">
@@ -5113,10 +5119,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -5125,14 +5131,14 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
+        <v>255</v>
+      </c>
+      <c r="O14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s">
         <v>256</v>
       </c>
-      <c r="O14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P14" t="s">
-        <v>257</v>
-      </c>
       <c r="Q14" t="s">
         <v>25</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="2:19">
@@ -5148,10 +5154,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -5160,14 +5166,14 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O15" t="s">
+        <v>234</v>
+      </c>
+      <c r="P15" t="s">
         <v>258</v>
       </c>
-      <c r="O15" t="s">
-        <v>235</v>
-      </c>
-      <c r="P15" t="s">
-        <v>259</v>
-      </c>
       <c r="Q15" t="s">
         <v>25</v>
       </c>
@@ -5175,7 +5181,7 @@
         <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="2:19">
@@ -5204,14 +5210,14 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
+        <v>259</v>
+      </c>
+      <c r="O16" t="s">
+        <v>234</v>
+      </c>
+      <c r="P16" t="s">
         <v>260</v>
       </c>
-      <c r="O16" t="s">
-        <v>235</v>
-      </c>
-      <c r="P16" t="s">
-        <v>261</v>
-      </c>
       <c r="Q16" t="s">
         <v>25</v>
       </c>
@@ -5219,7 +5225,7 @@
         <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="2:19">
@@ -5227,32 +5233,32 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" t="s">
         <v>231</v>
-      </c>
-      <c r="D17" t="s">
-        <v>232</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
       </c>
       <c r="F17" t="s">
+        <v>232</v>
+      </c>
+      <c r="G17" t="s">
         <v>233</v>
       </c>
-      <c r="G17" t="s">
-        <v>234</v>
-      </c>
       <c r="M17" t="s">
         <v>17</v>
       </c>
       <c r="N17" t="s">
+        <v>261</v>
+      </c>
+      <c r="O17" t="s">
+        <v>234</v>
+      </c>
+      <c r="P17" t="s">
         <v>262</v>
       </c>
-      <c r="O17" t="s">
-        <v>235</v>
-      </c>
-      <c r="P17" t="s">
-        <v>263</v>
-      </c>
       <c r="Q17" t="s">
         <v>25</v>
       </c>
@@ -5260,7 +5266,7 @@
         <v>35</v>
       </c>
       <c r="S17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="2:19">
@@ -5268,10 +5274,10 @@
         <v>34</v>
       </c>
       <c r="C18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" t="s">
         <v>203</v>
-      </c>
-      <c r="D18" t="s">
-        <v>204</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -5280,14 +5286,14 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
+        <v>263</v>
+      </c>
+      <c r="O18" t="s">
+        <v>234</v>
+      </c>
+      <c r="P18" t="s">
         <v>264</v>
       </c>
-      <c r="O18" t="s">
-        <v>235</v>
-      </c>
-      <c r="P18" t="s">
-        <v>265</v>
-      </c>
       <c r="Q18" t="s">
         <v>25</v>
       </c>
@@ -5295,7 +5301,7 @@
         <v>35</v>
       </c>
       <c r="S18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -5315,14 +5321,14 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O19" t="s">
+        <v>234</v>
+      </c>
+      <c r="P19" t="s">
         <v>266</v>
       </c>
-      <c r="O19" t="s">
-        <v>235</v>
-      </c>
-      <c r="P19" t="s">
-        <v>267</v>
-      </c>
       <c r="Q19" t="s">
         <v>25</v>
       </c>
@@ -5330,7 +5336,7 @@
         <v>35</v>
       </c>
       <c r="S19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="2:19">
@@ -5350,14 +5356,14 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
+        <v>267</v>
+      </c>
+      <c r="O20" t="s">
+        <v>234</v>
+      </c>
+      <c r="P20" t="s">
         <v>268</v>
       </c>
-      <c r="O20" t="s">
-        <v>235</v>
-      </c>
-      <c r="P20" t="s">
-        <v>269</v>
-      </c>
       <c r="Q20" t="s">
         <v>25</v>
       </c>
@@ -5365,7 +5371,7 @@
         <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="2:19">
@@ -5385,14 +5391,14 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
+        <v>269</v>
+      </c>
+      <c r="O21" t="s">
+        <v>234</v>
+      </c>
+      <c r="P21" t="s">
         <v>270</v>
       </c>
-      <c r="O21" t="s">
-        <v>235</v>
-      </c>
-      <c r="P21" t="s">
-        <v>271</v>
-      </c>
       <c r="Q21" t="s">
         <v>25</v>
       </c>
@@ -5400,7 +5406,7 @@
         <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="2:19">
@@ -5408,10 +5414,10 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="s">
         <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -5426,14 +5432,14 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
+        <v>271</v>
+      </c>
+      <c r="O22" t="s">
+        <v>234</v>
+      </c>
+      <c r="P22" t="s">
         <v>272</v>
       </c>
-      <c r="O22" t="s">
-        <v>235</v>
-      </c>
-      <c r="P22" t="s">
-        <v>273</v>
-      </c>
       <c r="Q22" t="s">
         <v>25</v>
       </c>
@@ -5441,34 +5447,34 @@
         <v>35</v>
       </c>
       <c r="S22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
         <v>193</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>194</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>195</v>
       </c>
-      <c r="E23" t="s">
-        <v>196</v>
-      </c>
       <c r="M23" t="s">
         <v>17</v>
       </c>
       <c r="N23" t="s">
+        <v>273</v>
+      </c>
+      <c r="O23" t="s">
+        <v>234</v>
+      </c>
+      <c r="P23" t="s">
         <v>274</v>
       </c>
-      <c r="O23" t="s">
-        <v>235</v>
-      </c>
-      <c r="P23" t="s">
-        <v>275</v>
-      </c>
       <c r="Q23" t="s">
         <v>25</v>
       </c>
@@ -5476,31 +5482,31 @@
         <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M24" t="s">
         <v>17</v>
       </c>
       <c r="N24" t="s">
+        <v>275</v>
+      </c>
+      <c r="O24" t="s">
+        <v>234</v>
+      </c>
+      <c r="P24" t="s">
         <v>276</v>
       </c>
-      <c r="O24" t="s">
-        <v>235</v>
-      </c>
-      <c r="P24" t="s">
-        <v>277</v>
-      </c>
       <c r="Q24" t="s">
         <v>25</v>
       </c>
@@ -5508,31 +5514,31 @@
         <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M25" t="s">
         <v>17</v>
       </c>
       <c r="N25" t="s">
+        <v>277</v>
+      </c>
+      <c r="O25" t="s">
+        <v>234</v>
+      </c>
+      <c r="P25" t="s">
         <v>278</v>
       </c>
-      <c r="O25" t="s">
-        <v>235</v>
-      </c>
-      <c r="P25" t="s">
-        <v>279</v>
-      </c>
       <c r="Q25" t="s">
         <v>25</v>
       </c>
@@ -5540,7 +5546,7 @@
         <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -5548,14 +5554,14 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
+        <v>279</v>
+      </c>
+      <c r="O26" t="s">
+        <v>234</v>
+      </c>
+      <c r="P26" t="s">
         <v>280</v>
       </c>
-      <c r="O26" t="s">
-        <v>235</v>
-      </c>
-      <c r="P26" t="s">
-        <v>281</v>
-      </c>
       <c r="Q26" t="s">
         <v>25</v>
       </c>
@@ -5563,7 +5569,7 @@
         <v>35</v>
       </c>
       <c r="S26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="2:19">
@@ -5571,14 +5577,14 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
+        <v>281</v>
+      </c>
+      <c r="O27" t="s">
+        <v>234</v>
+      </c>
+      <c r="P27" t="s">
         <v>282</v>
       </c>
-      <c r="O27" t="s">
-        <v>235</v>
-      </c>
-      <c r="P27" t="s">
-        <v>283</v>
-      </c>
       <c r="Q27" t="s">
         <v>25</v>
       </c>
@@ -5586,12 +5592,12 @@
         <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="2:19" ht="17.649999999999999" thickBot="1">
       <c r="B28" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -5599,14 +5605,14 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
+        <v>283</v>
+      </c>
+      <c r="O28" t="s">
+        <v>234</v>
+      </c>
+      <c r="P28" t="s">
         <v>284</v>
       </c>
-      <c r="O28" t="s">
-        <v>235</v>
-      </c>
-      <c r="P28" t="s">
-        <v>285</v>
-      </c>
       <c r="Q28" t="s">
         <v>25</v>
       </c>
@@ -5614,31 +5620,31 @@
         <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B29" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>
       <c r="N29" t="s">
+        <v>285</v>
+      </c>
+      <c r="O29" t="s">
+        <v>234</v>
+      </c>
+      <c r="P29" t="s">
         <v>286</v>
       </c>
-      <c r="O29" t="s">
-        <v>235</v>
-      </c>
-      <c r="P29" t="s">
-        <v>287</v>
-      </c>
       <c r="Q29" t="s">
         <v>25</v>
       </c>
@@ -5646,31 +5652,31 @@
         <v>35</v>
       </c>
       <c r="S29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
+        <v>287</v>
+      </c>
+      <c r="O30" t="s">
+        <v>234</v>
+      </c>
+      <c r="P30" t="s">
         <v>288</v>
       </c>
-      <c r="O30" t="s">
-        <v>235</v>
-      </c>
-      <c r="P30" t="s">
-        <v>289</v>
-      </c>
       <c r="Q30" t="s">
         <v>25</v>
       </c>
@@ -5678,7 +5684,7 @@
         <v>35</v>
       </c>
       <c r="S30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="2:19">
@@ -5686,14 +5692,14 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
+        <v>289</v>
+      </c>
+      <c r="O31" t="s">
+        <v>234</v>
+      </c>
+      <c r="P31" t="s">
         <v>290</v>
       </c>
-      <c r="O31" t="s">
-        <v>235</v>
-      </c>
-      <c r="P31" t="s">
-        <v>291</v>
-      </c>
       <c r="Q31" t="s">
         <v>25</v>
       </c>
@@ -5701,7 +5707,7 @@
         <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="2:19">
@@ -5709,14 +5715,14 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
+        <v>291</v>
+      </c>
+      <c r="O32" t="s">
+        <v>234</v>
+      </c>
+      <c r="P32" t="s">
         <v>292</v>
       </c>
-      <c r="O32" t="s">
-        <v>235</v>
-      </c>
-      <c r="P32" t="s">
-        <v>293</v>
-      </c>
       <c r="Q32" t="s">
         <v>25</v>
       </c>
@@ -5724,7 +5730,7 @@
         <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="2:19">
@@ -5732,14 +5738,14 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
+        <v>293</v>
+      </c>
+      <c r="O33" t="s">
+        <v>234</v>
+      </c>
+      <c r="P33" t="s">
         <v>294</v>
       </c>
-      <c r="O33" t="s">
-        <v>235</v>
-      </c>
-      <c r="P33" t="s">
-        <v>295</v>
-      </c>
       <c r="Q33" t="s">
         <v>25</v>
       </c>
@@ -5747,7 +5753,7 @@
         <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="2:19">
@@ -5755,14 +5761,14 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
+        <v>295</v>
+      </c>
+      <c r="O34" t="s">
+        <v>234</v>
+      </c>
+      <c r="P34" t="s">
         <v>296</v>
       </c>
-      <c r="O34" t="s">
-        <v>235</v>
-      </c>
-      <c r="P34" t="s">
-        <v>297</v>
-      </c>
       <c r="Q34" t="s">
         <v>25</v>
       </c>
@@ -5770,7 +5776,7 @@
         <v>35</v>
       </c>
       <c r="S34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="2:19">
@@ -5778,14 +5784,14 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
+        <v>297</v>
+      </c>
+      <c r="O35" t="s">
+        <v>234</v>
+      </c>
+      <c r="P35" t="s">
         <v>298</v>
       </c>
-      <c r="O35" t="s">
-        <v>235</v>
-      </c>
-      <c r="P35" t="s">
-        <v>299</v>
-      </c>
       <c r="Q35" t="s">
         <v>25</v>
       </c>
@@ -5793,7 +5799,7 @@
         <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="2:19">
@@ -5801,14 +5807,14 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
+        <v>299</v>
+      </c>
+      <c r="O36" t="s">
+        <v>234</v>
+      </c>
+      <c r="P36" t="s">
         <v>300</v>
       </c>
-      <c r="O36" t="s">
-        <v>235</v>
-      </c>
-      <c r="P36" t="s">
-        <v>301</v>
-      </c>
       <c r="Q36" t="s">
         <v>25</v>
       </c>
@@ -5816,7 +5822,7 @@
         <v>35</v>
       </c>
       <c r="S36" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="2:19">
@@ -5824,14 +5830,14 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
+        <v>301</v>
+      </c>
+      <c r="O37" t="s">
+        <v>234</v>
+      </c>
+      <c r="P37" t="s">
         <v>302</v>
       </c>
-      <c r="O37" t="s">
-        <v>235</v>
-      </c>
-      <c r="P37" t="s">
-        <v>303</v>
-      </c>
       <c r="Q37" t="s">
         <v>25</v>
       </c>
@@ -5839,7 +5845,7 @@
         <v>35</v>
       </c>
       <c r="S37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="17.649999999999999" thickBot="1">
@@ -5852,14 +5858,14 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
+        <v>303</v>
+      </c>
+      <c r="O38" t="s">
+        <v>234</v>
+      </c>
+      <c r="P38" t="s">
         <v>304</v>
       </c>
-      <c r="O38" t="s">
-        <v>235</v>
-      </c>
-      <c r="P38" t="s">
-        <v>305</v>
-      </c>
       <c r="Q38" t="s">
         <v>25</v>
       </c>
@@ -5867,12 +5873,12 @@
         <v>35</v>
       </c>
       <c r="S38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B39" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>10</v>
@@ -5887,20 +5893,20 @@
         <v>13</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M39" t="s">
         <v>17</v>
       </c>
       <c r="N39" t="s">
+        <v>305</v>
+      </c>
+      <c r="O39" t="s">
+        <v>234</v>
+      </c>
+      <c r="P39" t="s">
         <v>306</v>
       </c>
-      <c r="O39" t="s">
-        <v>235</v>
-      </c>
-      <c r="P39" t="s">
-        <v>307</v>
-      </c>
       <c r="Q39" t="s">
         <v>25</v>
       </c>
@@ -5908,7 +5914,7 @@
         <v>35</v>
       </c>
       <c r="S39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="2:19">
@@ -5916,17 +5922,17 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
+        <v>220</v>
+      </c>
+      <c r="D40" t="s">
         <v>221</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" t="s">
         <v>222</v>
       </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" t="s">
-        <v>223</v>
-      </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
@@ -5934,14 +5940,14 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
+        <v>307</v>
+      </c>
+      <c r="O40" t="s">
+        <v>234</v>
+      </c>
+      <c r="P40" t="s">
         <v>308</v>
       </c>
-      <c r="O40" t="s">
-        <v>235</v>
-      </c>
-      <c r="P40" t="s">
-        <v>309</v>
-      </c>
       <c r="Q40" t="s">
         <v>25</v>
       </c>
@@ -5949,21 +5955,21 @@
         <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="2:19">
       <c r="C41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" t="s">
         <v>224</v>
       </c>
-      <c r="D41" t="s">
-        <v>225</v>
-      </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -5972,14 +5978,14 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
+        <v>309</v>
+      </c>
+      <c r="O41" t="s">
+        <v>234</v>
+      </c>
+      <c r="P41" t="s">
         <v>310</v>
       </c>
-      <c r="O41" t="s">
-        <v>235</v>
-      </c>
-      <c r="P41" t="s">
-        <v>311</v>
-      </c>
       <c r="Q41" t="s">
         <v>25</v>
       </c>
@@ -5987,37 +5993,37 @@
         <v>35</v>
       </c>
       <c r="S41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="2:19">
       <c r="B42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" t="s">
         <v>226</v>
       </c>
-      <c r="D42" t="s">
-        <v>227</v>
-      </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M42" t="s">
         <v>17</v>
       </c>
       <c r="N42" t="s">
+        <v>311</v>
+      </c>
+      <c r="O42" t="s">
+        <v>234</v>
+      </c>
+      <c r="P42" t="s">
         <v>312</v>
       </c>
-      <c r="O42" t="s">
-        <v>235</v>
-      </c>
-      <c r="P42" t="s">
-        <v>313</v>
-      </c>
       <c r="Q42" t="s">
         <v>25</v>
       </c>
@@ -6025,34 +6031,34 @@
         <v>35</v>
       </c>
       <c r="S42" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="2:19">
       <c r="C43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" t="s">
         <v>228</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>229</v>
       </c>
-      <c r="E43" t="s">
-        <v>230</v>
-      </c>
       <c r="F43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M43" t="s">
         <v>17</v>
       </c>
       <c r="N43" t="s">
+        <v>313</v>
+      </c>
+      <c r="O43" t="s">
+        <v>234</v>
+      </c>
+      <c r="P43" t="s">
         <v>314</v>
       </c>
-      <c r="O43" t="s">
-        <v>235</v>
-      </c>
-      <c r="P43" t="s">
-        <v>315</v>
-      </c>
       <c r="Q43" t="s">
         <v>25</v>
       </c>
@@ -6060,7 +6066,7 @@
         <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="2:19">
@@ -6068,14 +6074,14 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
+        <v>315</v>
+      </c>
+      <c r="O44" t="s">
+        <v>234</v>
+      </c>
+      <c r="P44" t="s">
         <v>316</v>
       </c>
-      <c r="O44" t="s">
-        <v>235</v>
-      </c>
-      <c r="P44" t="s">
-        <v>317</v>
-      </c>
       <c r="Q44" t="s">
         <v>25</v>
       </c>
@@ -6083,7 +6089,7 @@
         <v>35</v>
       </c>
       <c r="S44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="2:19">
@@ -6091,14 +6097,14 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
+        <v>317</v>
+      </c>
+      <c r="O45" t="s">
+        <v>234</v>
+      </c>
+      <c r="P45" t="s">
         <v>318</v>
       </c>
-      <c r="O45" t="s">
-        <v>235</v>
-      </c>
-      <c r="P45" t="s">
-        <v>319</v>
-      </c>
       <c r="Q45" t="s">
         <v>25</v>
       </c>
@@ -6106,7 +6112,7 @@
         <v>35</v>
       </c>
       <c r="S45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="2:19">
@@ -6114,14 +6120,14 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
+        <v>319</v>
+      </c>
+      <c r="O46" t="s">
+        <v>234</v>
+      </c>
+      <c r="P46" t="s">
         <v>320</v>
       </c>
-      <c r="O46" t="s">
-        <v>235</v>
-      </c>
-      <c r="P46" t="s">
-        <v>321</v>
-      </c>
       <c r="Q46" t="s">
         <v>25</v>
       </c>
@@ -6129,7 +6135,7 @@
         <v>35</v>
       </c>
       <c r="S46" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="2:19">
@@ -6137,14 +6143,14 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
+        <v>321</v>
+      </c>
+      <c r="O47" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" t="s">
         <v>322</v>
       </c>
-      <c r="O47" t="s">
-        <v>235</v>
-      </c>
-      <c r="P47" t="s">
-        <v>323</v>
-      </c>
       <c r="Q47" t="s">
         <v>25</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="2:19">
@@ -6160,14 +6166,14 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
+        <v>323</v>
+      </c>
+      <c r="O48" t="s">
+        <v>234</v>
+      </c>
+      <c r="P48" t="s">
         <v>324</v>
       </c>
-      <c r="O48" t="s">
-        <v>235</v>
-      </c>
-      <c r="P48" t="s">
-        <v>325</v>
-      </c>
       <c r="Q48" t="s">
         <v>25</v>
       </c>
@@ -6175,7 +6181,7 @@
         <v>35</v>
       </c>
       <c r="S48" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="13:19">
@@ -6183,14 +6189,14 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
+        <v>325</v>
+      </c>
+      <c r="O49" t="s">
+        <v>234</v>
+      </c>
+      <c r="P49" t="s">
         <v>326</v>
       </c>
-      <c r="O49" t="s">
-        <v>235</v>
-      </c>
-      <c r="P49" t="s">
-        <v>327</v>
-      </c>
       <c r="Q49" t="s">
         <v>25</v>
       </c>
@@ -6198,7 +6204,7 @@
         <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="13:19">
@@ -6206,14 +6212,14 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
+        <v>327</v>
+      </c>
+      <c r="O50" t="s">
+        <v>234</v>
+      </c>
+      <c r="P50" t="s">
         <v>328</v>
       </c>
-      <c r="O50" t="s">
-        <v>235</v>
-      </c>
-      <c r="P50" t="s">
-        <v>329</v>
-      </c>
       <c r="Q50" t="s">
         <v>25</v>
       </c>
@@ -6221,7 +6227,7 @@
         <v>35</v>
       </c>
       <c r="S50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="13:19">
@@ -6229,14 +6235,14 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
+        <v>329</v>
+      </c>
+      <c r="O51" t="s">
+        <v>234</v>
+      </c>
+      <c r="P51" t="s">
         <v>330</v>
       </c>
-      <c r="O51" t="s">
-        <v>235</v>
-      </c>
-      <c r="P51" t="s">
-        <v>331</v>
-      </c>
       <c r="Q51" t="s">
         <v>25</v>
       </c>
@@ -6244,7 +6250,7 @@
         <v>35</v>
       </c>
       <c r="S51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="13:19">
@@ -6252,14 +6258,14 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
+        <v>331</v>
+      </c>
+      <c r="O52" t="s">
+        <v>234</v>
+      </c>
+      <c r="P52" t="s">
         <v>332</v>
       </c>
-      <c r="O52" t="s">
-        <v>235</v>
-      </c>
-      <c r="P52" t="s">
-        <v>333</v>
-      </c>
       <c r="Q52" t="s">
         <v>25</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="13:19">
@@ -6275,14 +6281,14 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
+        <v>333</v>
+      </c>
+      <c r="O53" t="s">
+        <v>234</v>
+      </c>
+      <c r="P53" t="s">
         <v>334</v>
       </c>
-      <c r="O53" t="s">
-        <v>235</v>
-      </c>
-      <c r="P53" t="s">
-        <v>335</v>
-      </c>
       <c r="Q53" t="s">
         <v>25</v>
       </c>
@@ -6290,7 +6296,7 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="13:19">
@@ -6298,14 +6304,14 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
+        <v>335</v>
+      </c>
+      <c r="O54" t="s">
+        <v>234</v>
+      </c>
+      <c r="P54" t="s">
         <v>336</v>
       </c>
-      <c r="O54" t="s">
-        <v>235</v>
-      </c>
-      <c r="P54" t="s">
-        <v>337</v>
-      </c>
       <c r="Q54" t="s">
         <v>25</v>
       </c>
@@ -6313,7 +6319,7 @@
         <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="13:19">
@@ -6321,14 +6327,14 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
+        <v>337</v>
+      </c>
+      <c r="O55" t="s">
+        <v>234</v>
+      </c>
+      <c r="P55" t="s">
         <v>338</v>
       </c>
-      <c r="O55" t="s">
-        <v>235</v>
-      </c>
-      <c r="P55" t="s">
-        <v>339</v>
-      </c>
       <c r="Q55" t="s">
         <v>25</v>
       </c>
@@ -6336,7 +6342,7 @@
         <v>35</v>
       </c>
       <c r="S55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="13:19">
@@ -6344,14 +6350,14 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
+        <v>339</v>
+      </c>
+      <c r="O56" t="s">
+        <v>234</v>
+      </c>
+      <c r="P56" t="s">
         <v>340</v>
       </c>
-      <c r="O56" t="s">
-        <v>235</v>
-      </c>
-      <c r="P56" t="s">
-        <v>341</v>
-      </c>
       <c r="Q56" t="s">
         <v>25</v>
       </c>
@@ -6359,7 +6365,7 @@
         <v>35</v>
       </c>
       <c r="S56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="13:19">
@@ -6367,14 +6373,14 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
+        <v>341</v>
+      </c>
+      <c r="O57" t="s">
+        <v>234</v>
+      </c>
+      <c r="P57" t="s">
         <v>342</v>
       </c>
-      <c r="O57" t="s">
-        <v>235</v>
-      </c>
-      <c r="P57" t="s">
-        <v>343</v>
-      </c>
       <c r="Q57" t="s">
         <v>25</v>
       </c>
@@ -6382,7 +6388,7 @@
         <v>35</v>
       </c>
       <c r="S57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="13:19">
@@ -6390,14 +6396,14 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
+        <v>343</v>
+      </c>
+      <c r="O58" t="s">
+        <v>234</v>
+      </c>
+      <c r="P58" t="s">
         <v>344</v>
       </c>
-      <c r="O58" t="s">
-        <v>235</v>
-      </c>
-      <c r="P58" t="s">
-        <v>345</v>
-      </c>
       <c r="Q58" t="s">
         <v>25</v>
       </c>
@@ -6405,7 +6411,7 @@
         <v>35</v>
       </c>
       <c r="S58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="13:19">
@@ -6413,14 +6419,14 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
+        <v>345</v>
+      </c>
+      <c r="O59" t="s">
+        <v>234</v>
+      </c>
+      <c r="P59" t="s">
         <v>346</v>
       </c>
-      <c r="O59" t="s">
-        <v>235</v>
-      </c>
-      <c r="P59" t="s">
-        <v>347</v>
-      </c>
       <c r="Q59" t="s">
         <v>25</v>
       </c>
@@ -6428,7 +6434,7 @@
         <v>35</v>
       </c>
       <c r="S59" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="13:19">
@@ -6436,14 +6442,14 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
+        <v>347</v>
+      </c>
+      <c r="O60" t="s">
+        <v>234</v>
+      </c>
+      <c r="P60" t="s">
         <v>348</v>
       </c>
-      <c r="O60" t="s">
-        <v>235</v>
-      </c>
-      <c r="P60" t="s">
-        <v>349</v>
-      </c>
       <c r="Q60" t="s">
         <v>25</v>
       </c>
@@ -6451,7 +6457,7 @@
         <v>35</v>
       </c>
       <c r="S60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="13:19">
@@ -6459,14 +6465,14 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
+        <v>349</v>
+      </c>
+      <c r="O61" t="s">
+        <v>234</v>
+      </c>
+      <c r="P61" t="s">
         <v>350</v>
       </c>
-      <c r="O61" t="s">
-        <v>235</v>
-      </c>
-      <c r="P61" t="s">
-        <v>351</v>
-      </c>
       <c r="Q61" t="s">
         <v>25</v>
       </c>
@@ -6474,7 +6480,7 @@
         <v>35</v>
       </c>
       <c r="S61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="13:19">
@@ -6482,14 +6488,14 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
+        <v>351</v>
+      </c>
+      <c r="O62" t="s">
+        <v>234</v>
+      </c>
+      <c r="P62" t="s">
         <v>352</v>
       </c>
-      <c r="O62" t="s">
-        <v>235</v>
-      </c>
-      <c r="P62" t="s">
-        <v>353</v>
-      </c>
       <c r="Q62" t="s">
         <v>25</v>
       </c>
@@ -6497,7 +6503,7 @@
         <v>35</v>
       </c>
       <c r="S62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="13:19">
@@ -6505,14 +6511,14 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
+        <v>353</v>
+      </c>
+      <c r="O63" t="s">
+        <v>234</v>
+      </c>
+      <c r="P63" t="s">
         <v>354</v>
       </c>
-      <c r="O63" t="s">
-        <v>235</v>
-      </c>
-      <c r="P63" t="s">
-        <v>355</v>
-      </c>
       <c r="Q63" t="s">
         <v>25</v>
       </c>
@@ -6520,7 +6526,7 @@
         <v>35</v>
       </c>
       <c r="S63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="13:19">
@@ -6528,14 +6534,14 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
+        <v>355</v>
+      </c>
+      <c r="O64" t="s">
+        <v>234</v>
+      </c>
+      <c r="P64" t="s">
         <v>356</v>
       </c>
-      <c r="O64" t="s">
-        <v>235</v>
-      </c>
-      <c r="P64" t="s">
-        <v>357</v>
-      </c>
       <c r="Q64" t="s">
         <v>25</v>
       </c>
@@ -6543,7 +6549,7 @@
         <v>35</v>
       </c>
       <c r="S64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="13:19">
@@ -6551,14 +6557,14 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
+        <v>357</v>
+      </c>
+      <c r="O65" t="s">
+        <v>234</v>
+      </c>
+      <c r="P65" t="s">
         <v>358</v>
       </c>
-      <c r="O65" t="s">
-        <v>235</v>
-      </c>
-      <c r="P65" t="s">
-        <v>359</v>
-      </c>
       <c r="Q65" t="s">
         <v>25</v>
       </c>
@@ -6566,7 +6572,7 @@
         <v>35</v>
       </c>
       <c r="S65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="13:19">
@@ -6574,14 +6580,14 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
+        <v>359</v>
+      </c>
+      <c r="O66" t="s">
+        <v>234</v>
+      </c>
+      <c r="P66" t="s">
         <v>360</v>
       </c>
-      <c r="O66" t="s">
-        <v>235</v>
-      </c>
-      <c r="P66" t="s">
-        <v>361</v>
-      </c>
       <c r="Q66" t="s">
         <v>25</v>
       </c>
@@ -6589,7 +6595,7 @@
         <v>35</v>
       </c>
       <c r="S66" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="13:19">
@@ -6597,14 +6603,14 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
+        <v>361</v>
+      </c>
+      <c r="O67" t="s">
+        <v>234</v>
+      </c>
+      <c r="P67" t="s">
         <v>362</v>
       </c>
-      <c r="O67" t="s">
-        <v>235</v>
-      </c>
-      <c r="P67" t="s">
-        <v>363</v>
-      </c>
       <c r="Q67" t="s">
         <v>25</v>
       </c>
@@ -6612,7 +6618,7 @@
         <v>35</v>
       </c>
       <c r="S67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="13:19">
@@ -6620,14 +6626,14 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
+        <v>363</v>
+      </c>
+      <c r="O68" t="s">
+        <v>234</v>
+      </c>
+      <c r="P68" t="s">
         <v>364</v>
       </c>
-      <c r="O68" t="s">
-        <v>235</v>
-      </c>
-      <c r="P68" t="s">
-        <v>365</v>
-      </c>
       <c r="Q68" t="s">
         <v>25</v>
       </c>
@@ -6635,7 +6641,7 @@
         <v>35</v>
       </c>
       <c r="S68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="13:19">
@@ -6643,14 +6649,14 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
+        <v>365</v>
+      </c>
+      <c r="O69" t="s">
+        <v>234</v>
+      </c>
+      <c r="P69" t="s">
         <v>366</v>
       </c>
-      <c r="O69" t="s">
-        <v>235</v>
-      </c>
-      <c r="P69" t="s">
-        <v>367</v>
-      </c>
       <c r="Q69" t="s">
         <v>25</v>
       </c>
@@ -6658,7 +6664,7 @@
         <v>35</v>
       </c>
       <c r="S69" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="13:19">
@@ -6666,14 +6672,14 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
+        <v>367</v>
+      </c>
+      <c r="O70" t="s">
+        <v>234</v>
+      </c>
+      <c r="P70" t="s">
         <v>368</v>
       </c>
-      <c r="O70" t="s">
-        <v>235</v>
-      </c>
-      <c r="P70" t="s">
-        <v>369</v>
-      </c>
       <c r="Q70" t="s">
         <v>25</v>
       </c>
@@ -6681,7 +6687,7 @@
         <v>35</v>
       </c>
       <c r="S70" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="13:19">
@@ -6689,14 +6695,14 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
+        <v>369</v>
+      </c>
+      <c r="O71" t="s">
+        <v>234</v>
+      </c>
+      <c r="P71" t="s">
         <v>370</v>
       </c>
-      <c r="O71" t="s">
-        <v>235</v>
-      </c>
-      <c r="P71" t="s">
-        <v>371</v>
-      </c>
       <c r="Q71" t="s">
         <v>25</v>
       </c>
@@ -6704,7 +6710,7 @@
         <v>35</v>
       </c>
       <c r="S71" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="13:19">
@@ -6712,14 +6718,14 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
+        <v>371</v>
+      </c>
+      <c r="O72" t="s">
+        <v>234</v>
+      </c>
+      <c r="P72" t="s">
         <v>372</v>
       </c>
-      <c r="O72" t="s">
-        <v>235</v>
-      </c>
-      <c r="P72" t="s">
-        <v>373</v>
-      </c>
       <c r="Q72" t="s">
         <v>25</v>
       </c>
@@ -6727,7 +6733,7 @@
         <v>35</v>
       </c>
       <c r="S72" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="13:19">
@@ -6735,14 +6741,14 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
+        <v>373</v>
+      </c>
+      <c r="O73" t="s">
+        <v>234</v>
+      </c>
+      <c r="P73" t="s">
         <v>374</v>
       </c>
-      <c r="O73" t="s">
-        <v>235</v>
-      </c>
-      <c r="P73" t="s">
-        <v>375</v>
-      </c>
       <c r="Q73" t="s">
         <v>25</v>
       </c>
@@ -6750,7 +6756,7 @@
         <v>35</v>
       </c>
       <c r="S73" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="13:19">
@@ -6758,14 +6764,14 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
+        <v>375</v>
+      </c>
+      <c r="O74" t="s">
+        <v>234</v>
+      </c>
+      <c r="P74" t="s">
         <v>376</v>
       </c>
-      <c r="O74" t="s">
-        <v>235</v>
-      </c>
-      <c r="P74" t="s">
-        <v>377</v>
-      </c>
       <c r="Q74" t="s">
         <v>25</v>
       </c>
@@ -6773,7 +6779,7 @@
         <v>35</v>
       </c>
       <c r="S74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="13:19">
@@ -6781,14 +6787,14 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
+        <v>377</v>
+      </c>
+      <c r="O75" t="s">
+        <v>234</v>
+      </c>
+      <c r="P75" t="s">
         <v>378</v>
       </c>
-      <c r="O75" t="s">
-        <v>235</v>
-      </c>
-      <c r="P75" t="s">
-        <v>379</v>
-      </c>
       <c r="Q75" t="s">
         <v>25</v>
       </c>
@@ -6796,7 +6802,7 @@
         <v>35</v>
       </c>
       <c r="S75" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="13:19">
@@ -6804,14 +6810,14 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
+        <v>379</v>
+      </c>
+      <c r="O76" t="s">
+        <v>234</v>
+      </c>
+      <c r="P76" t="s">
         <v>380</v>
       </c>
-      <c r="O76" t="s">
-        <v>235</v>
-      </c>
-      <c r="P76" t="s">
-        <v>381</v>
-      </c>
       <c r="Q76" t="s">
         <v>25</v>
       </c>
@@ -6819,7 +6825,7 @@
         <v>35</v>
       </c>
       <c r="S76" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="13:19">
@@ -6827,14 +6833,14 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
+        <v>381</v>
+      </c>
+      <c r="O77" t="s">
+        <v>234</v>
+      </c>
+      <c r="P77" t="s">
         <v>382</v>
       </c>
-      <c r="O77" t="s">
-        <v>235</v>
-      </c>
-      <c r="P77" t="s">
-        <v>383</v>
-      </c>
       <c r="Q77" t="s">
         <v>25</v>
       </c>
@@ -6842,7 +6848,7 @@
         <v>35</v>
       </c>
       <c r="S77" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="13:19">
@@ -6850,14 +6856,14 @@
         <v>17</v>
       </c>
       <c r="N78" t="s">
+        <v>383</v>
+      </c>
+      <c r="O78" t="s">
+        <v>234</v>
+      </c>
+      <c r="P78" t="s">
         <v>384</v>
       </c>
-      <c r="O78" t="s">
-        <v>235</v>
-      </c>
-      <c r="P78" t="s">
-        <v>385</v>
-      </c>
       <c r="Q78" t="s">
         <v>25</v>
       </c>
@@ -6865,7 +6871,7 @@
         <v>35</v>
       </c>
       <c r="S78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="13:19">
@@ -6873,14 +6879,14 @@
         <v>17</v>
       </c>
       <c r="N79" t="s">
+        <v>385</v>
+      </c>
+      <c r="O79" t="s">
+        <v>234</v>
+      </c>
+      <c r="P79" t="s">
         <v>386</v>
       </c>
-      <c r="O79" t="s">
-        <v>235</v>
-      </c>
-      <c r="P79" t="s">
-        <v>387</v>
-      </c>
       <c r="Q79" t="s">
         <v>25</v>
       </c>
@@ -6888,7 +6894,7 @@
         <v>35</v>
       </c>
       <c r="S79" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="13:19">
@@ -6896,14 +6902,14 @@
         <v>17</v>
       </c>
       <c r="N80" t="s">
+        <v>387</v>
+      </c>
+      <c r="O80" t="s">
+        <v>234</v>
+      </c>
+      <c r="P80" t="s">
         <v>388</v>
       </c>
-      <c r="O80" t="s">
-        <v>235</v>
-      </c>
-      <c r="P80" t="s">
-        <v>389</v>
-      </c>
       <c r="Q80" t="s">
         <v>25</v>
       </c>
@@ -6911,7 +6917,7 @@
         <v>35</v>
       </c>
       <c r="S80" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="13:19">
@@ -6919,14 +6925,14 @@
         <v>17</v>
       </c>
       <c r="N81" t="s">
+        <v>389</v>
+      </c>
+      <c r="O81" t="s">
+        <v>234</v>
+      </c>
+      <c r="P81" t="s">
         <v>390</v>
       </c>
-      <c r="O81" t="s">
-        <v>235</v>
-      </c>
-      <c r="P81" t="s">
-        <v>391</v>
-      </c>
       <c r="Q81" t="s">
         <v>25</v>
       </c>
@@ -6934,7 +6940,7 @@
         <v>35</v>
       </c>
       <c r="S81" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="13:19">
@@ -6942,14 +6948,14 @@
         <v>17</v>
       </c>
       <c r="N82" t="s">
+        <v>391</v>
+      </c>
+      <c r="O82" t="s">
+        <v>234</v>
+      </c>
+      <c r="P82" t="s">
         <v>392</v>
       </c>
-      <c r="O82" t="s">
-        <v>235</v>
-      </c>
-      <c r="P82" t="s">
-        <v>393</v>
-      </c>
       <c r="Q82" t="s">
         <v>25</v>
       </c>
@@ -6957,7 +6963,7 @@
         <v>35</v>
       </c>
       <c r="S82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="13:19">
@@ -6965,14 +6971,14 @@
         <v>17</v>
       </c>
       <c r="N83" t="s">
+        <v>393</v>
+      </c>
+      <c r="O83" t="s">
+        <v>234</v>
+      </c>
+      <c r="P83" t="s">
         <v>394</v>
       </c>
-      <c r="O83" t="s">
-        <v>235</v>
-      </c>
-      <c r="P83" t="s">
-        <v>395</v>
-      </c>
       <c r="Q83" t="s">
         <v>25</v>
       </c>
@@ -6980,7 +6986,7 @@
         <v>35</v>
       </c>
       <c r="S83" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" spans="13:19">
@@ -6988,14 +6994,14 @@
         <v>17</v>
       </c>
       <c r="N84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O84" t="s">
+        <v>234</v>
+      </c>
+      <c r="P84" t="s">
         <v>396</v>
       </c>
-      <c r="O84" t="s">
-        <v>235</v>
-      </c>
-      <c r="P84" t="s">
-        <v>397</v>
-      </c>
       <c r="Q84" t="s">
         <v>25</v>
       </c>
@@ -7003,7 +7009,7 @@
         <v>35</v>
       </c>
       <c r="S84" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="13:19">
@@ -7011,14 +7017,14 @@
         <v>17</v>
       </c>
       <c r="N85" t="s">
+        <v>397</v>
+      </c>
+      <c r="O85" t="s">
+        <v>234</v>
+      </c>
+      <c r="P85" t="s">
         <v>398</v>
       </c>
-      <c r="O85" t="s">
-        <v>235</v>
-      </c>
-      <c r="P85" t="s">
-        <v>399</v>
-      </c>
       <c r="Q85" t="s">
         <v>25</v>
       </c>
@@ -7026,7 +7032,7 @@
         <v>35</v>
       </c>
       <c r="S85" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="13:19">
@@ -7034,14 +7040,14 @@
         <v>17</v>
       </c>
       <c r="N86" t="s">
+        <v>399</v>
+      </c>
+      <c r="O86" t="s">
+        <v>234</v>
+      </c>
+      <c r="P86" t="s">
         <v>400</v>
       </c>
-      <c r="O86" t="s">
-        <v>235</v>
-      </c>
-      <c r="P86" t="s">
-        <v>401</v>
-      </c>
       <c r="Q86" t="s">
         <v>25</v>
       </c>
@@ -7049,7 +7055,7 @@
         <v>35</v>
       </c>
       <c r="S86" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="13:19">
@@ -7057,14 +7063,14 @@
         <v>17</v>
       </c>
       <c r="N87" t="s">
+        <v>401</v>
+      </c>
+      <c r="O87" t="s">
+        <v>234</v>
+      </c>
+      <c r="P87" t="s">
         <v>402</v>
       </c>
-      <c r="O87" t="s">
-        <v>235</v>
-      </c>
-      <c r="P87" t="s">
-        <v>403</v>
-      </c>
       <c r="Q87" t="s">
         <v>25</v>
       </c>
@@ -7072,7 +7078,7 @@
         <v>35</v>
       </c>
       <c r="S87" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="13:19">
@@ -7080,14 +7086,14 @@
         <v>17</v>
       </c>
       <c r="N88" t="s">
+        <v>403</v>
+      </c>
+      <c r="O88" t="s">
+        <v>234</v>
+      </c>
+      <c r="P88" t="s">
         <v>404</v>
       </c>
-      <c r="O88" t="s">
-        <v>235</v>
-      </c>
-      <c r="P88" t="s">
-        <v>405</v>
-      </c>
       <c r="Q88" t="s">
         <v>25</v>
       </c>
@@ -7095,7 +7101,7 @@
         <v>35</v>
       </c>
       <c r="S88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="13:19">
@@ -7103,14 +7109,14 @@
         <v>17</v>
       </c>
       <c r="N89" t="s">
+        <v>405</v>
+      </c>
+      <c r="O89" t="s">
+        <v>234</v>
+      </c>
+      <c r="P89" t="s">
         <v>406</v>
       </c>
-      <c r="O89" t="s">
-        <v>235</v>
-      </c>
-      <c r="P89" t="s">
-        <v>407</v>
-      </c>
       <c r="Q89" t="s">
         <v>25</v>
       </c>
@@ -7118,7 +7124,7 @@
         <v>35</v>
       </c>
       <c r="S89" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="13:19">
@@ -7126,14 +7132,14 @@
         <v>17</v>
       </c>
       <c r="N90" t="s">
+        <v>407</v>
+      </c>
+      <c r="O90" t="s">
+        <v>234</v>
+      </c>
+      <c r="P90" t="s">
         <v>408</v>
       </c>
-      <c r="O90" t="s">
-        <v>235</v>
-      </c>
-      <c r="P90" t="s">
-        <v>409</v>
-      </c>
       <c r="Q90" t="s">
         <v>25</v>
       </c>
@@ -7141,7 +7147,7 @@
         <v>35</v>
       </c>
       <c r="S90" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="13:19">
@@ -7149,14 +7155,14 @@
         <v>17</v>
       </c>
       <c r="N91" t="s">
+        <v>409</v>
+      </c>
+      <c r="O91" t="s">
+        <v>234</v>
+      </c>
+      <c r="P91" t="s">
         <v>410</v>
       </c>
-      <c r="O91" t="s">
-        <v>235</v>
-      </c>
-      <c r="P91" t="s">
-        <v>411</v>
-      </c>
       <c r="Q91" t="s">
         <v>25</v>
       </c>
@@ -7164,7 +7170,7 @@
         <v>35</v>
       </c>
       <c r="S91" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="13:19">
@@ -7172,14 +7178,14 @@
         <v>17</v>
       </c>
       <c r="N92" t="s">
+        <v>411</v>
+      </c>
+      <c r="O92" t="s">
+        <v>234</v>
+      </c>
+      <c r="P92" t="s">
         <v>412</v>
       </c>
-      <c r="O92" t="s">
-        <v>235</v>
-      </c>
-      <c r="P92" t="s">
-        <v>413</v>
-      </c>
       <c r="Q92" t="s">
         <v>25</v>
       </c>
@@ -7187,7 +7193,7 @@
         <v>35</v>
       </c>
       <c r="S92" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="13:19">
@@ -7195,14 +7201,14 @@
         <v>17</v>
       </c>
       <c r="N93" t="s">
+        <v>413</v>
+      </c>
+      <c r="O93" t="s">
+        <v>234</v>
+      </c>
+      <c r="P93" t="s">
         <v>414</v>
       </c>
-      <c r="O93" t="s">
-        <v>235</v>
-      </c>
-      <c r="P93" t="s">
-        <v>415</v>
-      </c>
       <c r="Q93" t="s">
         <v>25</v>
       </c>
@@ -7210,7 +7216,7 @@
         <v>35</v>
       </c>
       <c r="S93" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="13:19">
@@ -7218,14 +7224,14 @@
         <v>17</v>
       </c>
       <c r="N94" t="s">
+        <v>415</v>
+      </c>
+      <c r="O94" t="s">
+        <v>234</v>
+      </c>
+      <c r="P94" t="s">
         <v>416</v>
       </c>
-      <c r="O94" t="s">
-        <v>235</v>
-      </c>
-      <c r="P94" t="s">
-        <v>417</v>
-      </c>
       <c r="Q94" t="s">
         <v>25</v>
       </c>
@@ -7233,7 +7239,7 @@
         <v>35</v>
       </c>
       <c r="S94" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" spans="13:19">
@@ -7241,14 +7247,14 @@
         <v>17</v>
       </c>
       <c r="N95" t="s">
+        <v>417</v>
+      </c>
+      <c r="O95" t="s">
+        <v>234</v>
+      </c>
+      <c r="P95" t="s">
         <v>418</v>
       </c>
-      <c r="O95" t="s">
-        <v>235</v>
-      </c>
-      <c r="P95" t="s">
-        <v>419</v>
-      </c>
       <c r="Q95" t="s">
         <v>25</v>
       </c>
@@ -7256,7 +7262,7 @@
         <v>35</v>
       </c>
       <c r="S95" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" spans="13:19">
@@ -7264,14 +7270,14 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
+        <v>419</v>
+      </c>
+      <c r="O96" t="s">
+        <v>234</v>
+      </c>
+      <c r="P96" t="s">
         <v>420</v>
       </c>
-      <c r="O96" t="s">
-        <v>235</v>
-      </c>
-      <c r="P96" t="s">
-        <v>421</v>
-      </c>
       <c r="Q96" t="s">
         <v>25</v>
       </c>
@@ -7279,7 +7285,7 @@
         <v>35</v>
       </c>
       <c r="S96" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="13:19">
@@ -7287,14 +7293,14 @@
         <v>17</v>
       </c>
       <c r="N97" t="s">
+        <v>421</v>
+      </c>
+      <c r="O97" t="s">
+        <v>234</v>
+      </c>
+      <c r="P97" t="s">
         <v>422</v>
       </c>
-      <c r="O97" t="s">
-        <v>235</v>
-      </c>
-      <c r="P97" t="s">
-        <v>423</v>
-      </c>
       <c r="Q97" t="s">
         <v>25</v>
       </c>
@@ -7302,7 +7308,7 @@
         <v>35</v>
       </c>
       <c r="S97" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="13:19">
@@ -7310,14 +7316,14 @@
         <v>17</v>
       </c>
       <c r="N98" t="s">
+        <v>423</v>
+      </c>
+      <c r="O98" t="s">
+        <v>234</v>
+      </c>
+      <c r="P98" t="s">
         <v>424</v>
       </c>
-      <c r="O98" t="s">
-        <v>235</v>
-      </c>
-      <c r="P98" t="s">
-        <v>425</v>
-      </c>
       <c r="Q98" t="s">
         <v>25</v>
       </c>
@@ -7325,7 +7331,7 @@
         <v>35</v>
       </c>
       <c r="S98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="13:19">
@@ -7333,14 +7339,14 @@
         <v>17</v>
       </c>
       <c r="N99" t="s">
+        <v>425</v>
+      </c>
+      <c r="O99" t="s">
+        <v>234</v>
+      </c>
+      <c r="P99" t="s">
         <v>426</v>
       </c>
-      <c r="O99" t="s">
-        <v>235</v>
-      </c>
-      <c r="P99" t="s">
-        <v>427</v>
-      </c>
       <c r="Q99" t="s">
         <v>25</v>
       </c>
@@ -7348,7 +7354,7 @@
         <v>35</v>
       </c>
       <c r="S99" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" spans="13:19">
@@ -7356,14 +7362,14 @@
         <v>17</v>
       </c>
       <c r="N100" t="s">
+        <v>427</v>
+      </c>
+      <c r="O100" t="s">
+        <v>234</v>
+      </c>
+      <c r="P100" t="s">
         <v>428</v>
       </c>
-      <c r="O100" t="s">
-        <v>235</v>
-      </c>
-      <c r="P100" t="s">
-        <v>429</v>
-      </c>
       <c r="Q100" t="s">
         <v>25</v>
       </c>
@@ -7371,7 +7377,7 @@
         <v>35</v>
       </c>
       <c r="S100" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="13:19">
@@ -7379,14 +7385,14 @@
         <v>17</v>
       </c>
       <c r="N101" t="s">
+        <v>429</v>
+      </c>
+      <c r="O101" t="s">
+        <v>234</v>
+      </c>
+      <c r="P101" t="s">
         <v>430</v>
       </c>
-      <c r="O101" t="s">
-        <v>235</v>
-      </c>
-      <c r="P101" t="s">
-        <v>431</v>
-      </c>
       <c r="Q101" t="s">
         <v>25</v>
       </c>
@@ -7394,7 +7400,7 @@
         <v>35</v>
       </c>
       <c r="S101" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="102" spans="13:19">
@@ -7402,14 +7408,14 @@
         <v>17</v>
       </c>
       <c r="N102" t="s">
+        <v>431</v>
+      </c>
+      <c r="O102" t="s">
+        <v>234</v>
+      </c>
+      <c r="P102" t="s">
         <v>432</v>
       </c>
-      <c r="O102" t="s">
-        <v>235</v>
-      </c>
-      <c r="P102" t="s">
-        <v>433</v>
-      </c>
       <c r="Q102" t="s">
         <v>25</v>
       </c>
@@ -7417,7 +7423,7 @@
         <v>35</v>
       </c>
       <c r="S102" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="13:19">
@@ -7425,14 +7431,14 @@
         <v>17</v>
       </c>
       <c r="N103" t="s">
+        <v>433</v>
+      </c>
+      <c r="O103" t="s">
+        <v>234</v>
+      </c>
+      <c r="P103" t="s">
         <v>434</v>
       </c>
-      <c r="O103" t="s">
-        <v>235</v>
-      </c>
-      <c r="P103" t="s">
-        <v>435</v>
-      </c>
       <c r="Q103" t="s">
         <v>25</v>
       </c>
@@ -7440,7 +7446,7 @@
         <v>35</v>
       </c>
       <c r="S103" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="104" spans="13:19">
@@ -7448,14 +7454,14 @@
         <v>17</v>
       </c>
       <c r="N104" t="s">
+        <v>435</v>
+      </c>
+      <c r="O104" t="s">
+        <v>234</v>
+      </c>
+      <c r="P104" t="s">
         <v>436</v>
       </c>
-      <c r="O104" t="s">
-        <v>235</v>
-      </c>
-      <c r="P104" t="s">
-        <v>437</v>
-      </c>
       <c r="Q104" t="s">
         <v>25</v>
       </c>
@@ -7463,7 +7469,7 @@
         <v>35</v>
       </c>
       <c r="S104" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="13:19">
@@ -7471,14 +7477,14 @@
         <v>17</v>
       </c>
       <c r="N105" t="s">
+        <v>437</v>
+      </c>
+      <c r="O105" t="s">
+        <v>234</v>
+      </c>
+      <c r="P105" t="s">
         <v>438</v>
       </c>
-      <c r="O105" t="s">
-        <v>235</v>
-      </c>
-      <c r="P105" t="s">
-        <v>439</v>
-      </c>
       <c r="Q105" t="s">
         <v>25</v>
       </c>
@@ -7486,7 +7492,7 @@
         <v>35</v>
       </c>
       <c r="S105" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="13:19">
@@ -7494,14 +7500,14 @@
         <v>17</v>
       </c>
       <c r="N106" t="s">
+        <v>439</v>
+      </c>
+      <c r="O106" t="s">
+        <v>234</v>
+      </c>
+      <c r="P106" t="s">
         <v>440</v>
       </c>
-      <c r="O106" t="s">
-        <v>235</v>
-      </c>
-      <c r="P106" t="s">
-        <v>441</v>
-      </c>
       <c r="Q106" t="s">
         <v>25</v>
       </c>
@@ -7509,7 +7515,7 @@
         <v>35</v>
       </c>
       <c r="S106" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107" spans="13:19">
@@ -7517,14 +7523,14 @@
         <v>17</v>
       </c>
       <c r="N107" t="s">
+        <v>441</v>
+      </c>
+      <c r="O107" t="s">
+        <v>234</v>
+      </c>
+      <c r="P107" t="s">
         <v>442</v>
       </c>
-      <c r="O107" t="s">
-        <v>235</v>
-      </c>
-      <c r="P107" t="s">
-        <v>443</v>
-      </c>
       <c r="Q107" t="s">
         <v>25</v>
       </c>
@@ -7532,7 +7538,7 @@
         <v>35</v>
       </c>
       <c r="S107" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108" spans="13:19">
@@ -7540,14 +7546,14 @@
         <v>17</v>
       </c>
       <c r="N108" t="s">
+        <v>443</v>
+      </c>
+      <c r="O108" t="s">
+        <v>234</v>
+      </c>
+      <c r="P108" t="s">
         <v>444</v>
       </c>
-      <c r="O108" t="s">
-        <v>235</v>
-      </c>
-      <c r="P108" t="s">
-        <v>445</v>
-      </c>
       <c r="Q108" t="s">
         <v>25</v>
       </c>
@@ -7555,7 +7561,7 @@
         <v>35</v>
       </c>
       <c r="S108" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="13:19">
@@ -7563,14 +7569,14 @@
         <v>17</v>
       </c>
       <c r="N109" t="s">
+        <v>445</v>
+      </c>
+      <c r="O109" t="s">
+        <v>234</v>
+      </c>
+      <c r="P109" t="s">
         <v>446</v>
       </c>
-      <c r="O109" t="s">
-        <v>235</v>
-      </c>
-      <c r="P109" t="s">
-        <v>447</v>
-      </c>
       <c r="Q109" t="s">
         <v>25</v>
       </c>
@@ -7578,7 +7584,7 @@
         <v>35</v>
       </c>
       <c r="S109" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" spans="13:19">
@@ -7586,14 +7592,14 @@
         <v>17</v>
       </c>
       <c r="N110" t="s">
+        <v>447</v>
+      </c>
+      <c r="O110" t="s">
+        <v>234</v>
+      </c>
+      <c r="P110" t="s">
         <v>448</v>
       </c>
-      <c r="O110" t="s">
-        <v>235</v>
-      </c>
-      <c r="P110" t="s">
-        <v>449</v>
-      </c>
       <c r="Q110" t="s">
         <v>25</v>
       </c>
@@ -7601,7 +7607,7 @@
         <v>35</v>
       </c>
       <c r="S110" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="111" spans="13:19">
@@ -7609,14 +7615,14 @@
         <v>17</v>
       </c>
       <c r="N111" t="s">
+        <v>449</v>
+      </c>
+      <c r="O111" t="s">
+        <v>234</v>
+      </c>
+      <c r="P111" t="s">
         <v>450</v>
       </c>
-      <c r="O111" t="s">
-        <v>235</v>
-      </c>
-      <c r="P111" t="s">
-        <v>451</v>
-      </c>
       <c r="Q111" t="s">
         <v>25</v>
       </c>
@@ -7624,7 +7630,7 @@
         <v>35</v>
       </c>
       <c r="S111" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="112" spans="13:19">
@@ -7632,14 +7638,14 @@
         <v>17</v>
       </c>
       <c r="N112" t="s">
+        <v>451</v>
+      </c>
+      <c r="O112" t="s">
+        <v>234</v>
+      </c>
+      <c r="P112" t="s">
         <v>452</v>
       </c>
-      <c r="O112" t="s">
-        <v>235</v>
-      </c>
-      <c r="P112" t="s">
-        <v>453</v>
-      </c>
       <c r="Q112" t="s">
         <v>25</v>
       </c>
@@ -7647,7 +7653,7 @@
         <v>35</v>
       </c>
       <c r="S112" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="13:19">
@@ -7655,14 +7661,14 @@
         <v>17</v>
       </c>
       <c r="N113" t="s">
+        <v>453</v>
+      </c>
+      <c r="O113" t="s">
+        <v>234</v>
+      </c>
+      <c r="P113" t="s">
         <v>454</v>
       </c>
-      <c r="O113" t="s">
-        <v>235</v>
-      </c>
-      <c r="P113" t="s">
-        <v>455</v>
-      </c>
       <c r="Q113" t="s">
         <v>25</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>35</v>
       </c>
       <c r="S113" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" spans="13:19">
@@ -7678,14 +7684,14 @@
         <v>17</v>
       </c>
       <c r="N114" t="s">
+        <v>455</v>
+      </c>
+      <c r="O114" t="s">
+        <v>234</v>
+      </c>
+      <c r="P114" t="s">
         <v>456</v>
       </c>
-      <c r="O114" t="s">
-        <v>235</v>
-      </c>
-      <c r="P114" t="s">
-        <v>457</v>
-      </c>
       <c r="Q114" t="s">
         <v>25</v>
       </c>
@@ -7693,7 +7699,7 @@
         <v>35</v>
       </c>
       <c r="S114" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="115" spans="13:19">
@@ -7701,14 +7707,14 @@
         <v>17</v>
       </c>
       <c r="N115" t="s">
+        <v>457</v>
+      </c>
+      <c r="O115" t="s">
+        <v>234</v>
+      </c>
+      <c r="P115" t="s">
         <v>458</v>
       </c>
-      <c r="O115" t="s">
-        <v>235</v>
-      </c>
-      <c r="P115" t="s">
-        <v>459</v>
-      </c>
       <c r="Q115" t="s">
         <v>25</v>
       </c>
@@ -7716,7 +7722,7 @@
         <v>35</v>
       </c>
       <c r="S115" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="116" spans="13:19">
@@ -7724,14 +7730,14 @@
         <v>17</v>
       </c>
       <c r="N116" t="s">
+        <v>459</v>
+      </c>
+      <c r="O116" t="s">
+        <v>234</v>
+      </c>
+      <c r="P116" t="s">
         <v>460</v>
       </c>
-      <c r="O116" t="s">
-        <v>235</v>
-      </c>
-      <c r="P116" t="s">
-        <v>461</v>
-      </c>
       <c r="Q116" t="s">
         <v>25</v>
       </c>
@@ -7739,7 +7745,7 @@
         <v>35</v>
       </c>
       <c r="S116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="117" spans="13:19">
@@ -7747,14 +7753,14 @@
         <v>17</v>
       </c>
       <c r="N117" t="s">
+        <v>461</v>
+      </c>
+      <c r="O117" t="s">
+        <v>234</v>
+      </c>
+      <c r="P117" t="s">
         <v>462</v>
       </c>
-      <c r="O117" t="s">
-        <v>235</v>
-      </c>
-      <c r="P117" t="s">
-        <v>463</v>
-      </c>
       <c r="Q117" t="s">
         <v>25</v>
       </c>
@@ -7762,7 +7768,7 @@
         <v>35</v>
       </c>
       <c r="S117" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="118" spans="13:19">
@@ -7770,14 +7776,14 @@
         <v>17</v>
       </c>
       <c r="N118" t="s">
+        <v>463</v>
+      </c>
+      <c r="O118" t="s">
+        <v>234</v>
+      </c>
+      <c r="P118" t="s">
         <v>464</v>
       </c>
-      <c r="O118" t="s">
-        <v>235</v>
-      </c>
-      <c r="P118" t="s">
-        <v>465</v>
-      </c>
       <c r="Q118" t="s">
         <v>25</v>
       </c>
@@ -7785,7 +7791,7 @@
         <v>35</v>
       </c>
       <c r="S118" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="119" spans="13:19">
@@ -7793,14 +7799,14 @@
         <v>17</v>
       </c>
       <c r="N119" t="s">
+        <v>465</v>
+      </c>
+      <c r="O119" t="s">
+        <v>234</v>
+      </c>
+      <c r="P119" t="s">
         <v>466</v>
       </c>
-      <c r="O119" t="s">
-        <v>235</v>
-      </c>
-      <c r="P119" t="s">
-        <v>467</v>
-      </c>
       <c r="Q119" t="s">
         <v>25</v>
       </c>
@@ -7808,7 +7814,7 @@
         <v>35</v>
       </c>
       <c r="S119" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="120" spans="13:19">
@@ -7816,14 +7822,14 @@
         <v>17</v>
       </c>
       <c r="N120" t="s">
+        <v>467</v>
+      </c>
+      <c r="O120" t="s">
+        <v>234</v>
+      </c>
+      <c r="P120" t="s">
         <v>468</v>
       </c>
-      <c r="O120" t="s">
-        <v>235</v>
-      </c>
-      <c r="P120" t="s">
-        <v>469</v>
-      </c>
       <c r="Q120" t="s">
         <v>25</v>
       </c>
@@ -7831,7 +7837,7 @@
         <v>35</v>
       </c>
       <c r="S120" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="121" spans="13:19">
@@ -7839,14 +7845,14 @@
         <v>17</v>
       </c>
       <c r="N121" t="s">
+        <v>469</v>
+      </c>
+      <c r="O121" t="s">
+        <v>234</v>
+      </c>
+      <c r="P121" t="s">
         <v>470</v>
       </c>
-      <c r="O121" t="s">
-        <v>235</v>
-      </c>
-      <c r="P121" t="s">
-        <v>471</v>
-      </c>
       <c r="Q121" t="s">
         <v>25</v>
       </c>
@@ -7854,7 +7860,7 @@
         <v>35</v>
       </c>
       <c r="S121" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="122" spans="13:19">
@@ -7862,14 +7868,14 @@
         <v>17</v>
       </c>
       <c r="N122" t="s">
+        <v>471</v>
+      </c>
+      <c r="O122" t="s">
+        <v>234</v>
+      </c>
+      <c r="P122" t="s">
         <v>472</v>
       </c>
-      <c r="O122" t="s">
-        <v>235</v>
-      </c>
-      <c r="P122" t="s">
-        <v>473</v>
-      </c>
       <c r="Q122" t="s">
         <v>25</v>
       </c>
@@ -7877,7 +7883,7 @@
         <v>35</v>
       </c>
       <c r="S122" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" spans="13:19">
@@ -7885,14 +7891,14 @@
         <v>17</v>
       </c>
       <c r="N123" t="s">
+        <v>473</v>
+      </c>
+      <c r="O123" t="s">
+        <v>234</v>
+      </c>
+      <c r="P123" t="s">
         <v>474</v>
       </c>
-      <c r="O123" t="s">
-        <v>235</v>
-      </c>
-      <c r="P123" t="s">
-        <v>475</v>
-      </c>
       <c r="Q123" t="s">
         <v>25</v>
       </c>
@@ -7900,7 +7906,7 @@
         <v>35</v>
       </c>
       <c r="S123" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="13:19">
@@ -7908,14 +7914,14 @@
         <v>17</v>
       </c>
       <c r="N124" t="s">
+        <v>475</v>
+      </c>
+      <c r="O124" t="s">
+        <v>234</v>
+      </c>
+      <c r="P124" t="s">
         <v>476</v>
       </c>
-      <c r="O124" t="s">
-        <v>235</v>
-      </c>
-      <c r="P124" t="s">
-        <v>477</v>
-      </c>
       <c r="Q124" t="s">
         <v>25</v>
       </c>
@@ -7923,7 +7929,7 @@
         <v>35</v>
       </c>
       <c r="S124" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="13:19">
@@ -7931,14 +7937,14 @@
         <v>17</v>
       </c>
       <c r="N125" t="s">
+        <v>477</v>
+      </c>
+      <c r="O125" t="s">
+        <v>234</v>
+      </c>
+      <c r="P125" t="s">
         <v>478</v>
       </c>
-      <c r="O125" t="s">
-        <v>235</v>
-      </c>
-      <c r="P125" t="s">
-        <v>479</v>
-      </c>
       <c r="Q125" t="s">
         <v>25</v>
       </c>
@@ -7946,7 +7952,7 @@
         <v>35</v>
       </c>
       <c r="S125" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="13:19">
@@ -7954,14 +7960,14 @@
         <v>17</v>
       </c>
       <c r="N126" t="s">
+        <v>479</v>
+      </c>
+      <c r="O126" t="s">
+        <v>234</v>
+      </c>
+      <c r="P126" t="s">
         <v>480</v>
       </c>
-      <c r="O126" t="s">
-        <v>235</v>
-      </c>
-      <c r="P126" t="s">
-        <v>481</v>
-      </c>
       <c r="Q126" t="s">
         <v>25</v>
       </c>
@@ -7969,7 +7975,7 @@
         <v>35</v>
       </c>
       <c r="S126" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="127" spans="13:19">
@@ -7977,14 +7983,14 @@
         <v>17</v>
       </c>
       <c r="N127" t="s">
+        <v>481</v>
+      </c>
+      <c r="O127" t="s">
+        <v>234</v>
+      </c>
+      <c r="P127" t="s">
         <v>482</v>
       </c>
-      <c r="O127" t="s">
-        <v>235</v>
-      </c>
-      <c r="P127" t="s">
-        <v>483</v>
-      </c>
       <c r="Q127" t="s">
         <v>25</v>
       </c>
@@ -7992,7 +7998,7 @@
         <v>35</v>
       </c>
       <c r="S127" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="128" spans="13:19">
@@ -8000,14 +8006,14 @@
         <v>17</v>
       </c>
       <c r="N128" t="s">
+        <v>483</v>
+      </c>
+      <c r="O128" t="s">
+        <v>234</v>
+      </c>
+      <c r="P128" t="s">
         <v>484</v>
       </c>
-      <c r="O128" t="s">
-        <v>235</v>
-      </c>
-      <c r="P128" t="s">
-        <v>485</v>
-      </c>
       <c r="Q128" t="s">
         <v>25</v>
       </c>
@@ -8015,7 +8021,7 @@
         <v>35</v>
       </c>
       <c r="S128" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="13:19">
@@ -8023,14 +8029,14 @@
         <v>17</v>
       </c>
       <c r="N129" t="s">
+        <v>485</v>
+      </c>
+      <c r="O129" t="s">
+        <v>234</v>
+      </c>
+      <c r="P129" t="s">
         <v>486</v>
       </c>
-      <c r="O129" t="s">
-        <v>235</v>
-      </c>
-      <c r="P129" t="s">
-        <v>487</v>
-      </c>
       <c r="Q129" t="s">
         <v>25</v>
       </c>
@@ -8038,7 +8044,7 @@
         <v>35</v>
       </c>
       <c r="S129" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="130" spans="13:19">
@@ -8046,14 +8052,14 @@
         <v>17</v>
       </c>
       <c r="N130" t="s">
+        <v>487</v>
+      </c>
+      <c r="O130" t="s">
+        <v>234</v>
+      </c>
+      <c r="P130" t="s">
         <v>488</v>
       </c>
-      <c r="O130" t="s">
-        <v>235</v>
-      </c>
-      <c r="P130" t="s">
-        <v>489</v>
-      </c>
       <c r="Q130" t="s">
         <v>25</v>
       </c>
@@ -8061,7 +8067,7 @@
         <v>35</v>
       </c>
       <c r="S130" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131" spans="13:19">
@@ -8069,14 +8075,14 @@
         <v>17</v>
       </c>
       <c r="N131" t="s">
+        <v>489</v>
+      </c>
+      <c r="O131" t="s">
+        <v>234</v>
+      </c>
+      <c r="P131" t="s">
         <v>490</v>
       </c>
-      <c r="O131" t="s">
-        <v>235</v>
-      </c>
-      <c r="P131" t="s">
-        <v>491</v>
-      </c>
       <c r="Q131" t="s">
         <v>25</v>
       </c>
@@ -8084,7 +8090,7 @@
         <v>35</v>
       </c>
       <c r="S131" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="132" spans="13:19">
@@ -8092,14 +8098,14 @@
         <v>17</v>
       </c>
       <c r="N132" t="s">
+        <v>491</v>
+      </c>
+      <c r="O132" t="s">
+        <v>234</v>
+      </c>
+      <c r="P132" t="s">
         <v>492</v>
       </c>
-      <c r="O132" t="s">
-        <v>235</v>
-      </c>
-      <c r="P132" t="s">
-        <v>493</v>
-      </c>
       <c r="Q132" t="s">
         <v>25</v>
       </c>
@@ -8107,7 +8113,7 @@
         <v>35</v>
       </c>
       <c r="S132" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="13:19">
@@ -8115,14 +8121,14 @@
         <v>17</v>
       </c>
       <c r="N133" t="s">
+        <v>493</v>
+      </c>
+      <c r="O133" t="s">
+        <v>234</v>
+      </c>
+      <c r="P133" t="s">
         <v>494</v>
       </c>
-      <c r="O133" t="s">
-        <v>235</v>
-      </c>
-      <c r="P133" t="s">
-        <v>495</v>
-      </c>
       <c r="Q133" t="s">
         <v>25</v>
       </c>
@@ -8130,7 +8136,7 @@
         <v>35</v>
       </c>
       <c r="S133" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="13:19">
@@ -8138,14 +8144,14 @@
         <v>17</v>
       </c>
       <c r="N134" t="s">
+        <v>495</v>
+      </c>
+      <c r="O134" t="s">
+        <v>234</v>
+      </c>
+      <c r="P134" t="s">
         <v>496</v>
       </c>
-      <c r="O134" t="s">
-        <v>235</v>
-      </c>
-      <c r="P134" t="s">
-        <v>497</v>
-      </c>
       <c r="Q134" t="s">
         <v>25</v>
       </c>
@@ -8153,7 +8159,7 @@
         <v>35</v>
       </c>
       <c r="S134" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="135" spans="13:19">
@@ -8161,14 +8167,14 @@
         <v>17</v>
       </c>
       <c r="N135" t="s">
+        <v>497</v>
+      </c>
+      <c r="O135" t="s">
+        <v>234</v>
+      </c>
+      <c r="P135" t="s">
         <v>498</v>
       </c>
-      <c r="O135" t="s">
-        <v>235</v>
-      </c>
-      <c r="P135" t="s">
-        <v>499</v>
-      </c>
       <c r="Q135" t="s">
         <v>25</v>
       </c>
@@ -8176,7 +8182,7 @@
         <v>35</v>
       </c>
       <c r="S135" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="136" spans="13:19">
@@ -8184,14 +8190,14 @@
         <v>17</v>
       </c>
       <c r="N136" t="s">
+        <v>499</v>
+      </c>
+      <c r="O136" t="s">
+        <v>234</v>
+      </c>
+      <c r="P136" t="s">
         <v>500</v>
       </c>
-      <c r="O136" t="s">
-        <v>235</v>
-      </c>
-      <c r="P136" t="s">
-        <v>501</v>
-      </c>
       <c r="Q136" t="s">
         <v>25</v>
       </c>
@@ -8199,7 +8205,7 @@
         <v>35</v>
       </c>
       <c r="S136" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="137" spans="13:19">
@@ -8207,14 +8213,14 @@
         <v>17</v>
       </c>
       <c r="N137" t="s">
+        <v>501</v>
+      </c>
+      <c r="O137" t="s">
+        <v>234</v>
+      </c>
+      <c r="P137" t="s">
         <v>502</v>
       </c>
-      <c r="O137" t="s">
-        <v>235</v>
-      </c>
-      <c r="P137" t="s">
-        <v>503</v>
-      </c>
       <c r="Q137" t="s">
         <v>25</v>
       </c>
@@ -8222,7 +8228,7 @@
         <v>35</v>
       </c>
       <c r="S137" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="13:19">
@@ -8230,14 +8236,14 @@
         <v>17</v>
       </c>
       <c r="N138" t="s">
+        <v>503</v>
+      </c>
+      <c r="O138" t="s">
+        <v>234</v>
+      </c>
+      <c r="P138" t="s">
         <v>504</v>
       </c>
-      <c r="O138" t="s">
-        <v>235</v>
-      </c>
-      <c r="P138" t="s">
-        <v>505</v>
-      </c>
       <c r="Q138" t="s">
         <v>25</v>
       </c>
@@ -8245,7 +8251,7 @@
         <v>35</v>
       </c>
       <c r="S138" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="13:19">
@@ -8253,14 +8259,14 @@
         <v>17</v>
       </c>
       <c r="N139" t="s">
+        <v>505</v>
+      </c>
+      <c r="O139" t="s">
+        <v>234</v>
+      </c>
+      <c r="P139" t="s">
         <v>506</v>
       </c>
-      <c r="O139" t="s">
-        <v>235</v>
-      </c>
-      <c r="P139" t="s">
-        <v>507</v>
-      </c>
       <c r="Q139" t="s">
         <v>25</v>
       </c>
@@ -8268,7 +8274,7 @@
         <v>35</v>
       </c>
       <c r="S139" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="140" spans="13:19">
@@ -8276,14 +8282,14 @@
         <v>17</v>
       </c>
       <c r="N140" t="s">
+        <v>507</v>
+      </c>
+      <c r="O140" t="s">
+        <v>234</v>
+      </c>
+      <c r="P140" t="s">
         <v>508</v>
       </c>
-      <c r="O140" t="s">
-        <v>235</v>
-      </c>
-      <c r="P140" t="s">
-        <v>509</v>
-      </c>
       <c r="Q140" t="s">
         <v>25</v>
       </c>
@@ -8291,7 +8297,7 @@
         <v>35</v>
       </c>
       <c r="S140" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="141" spans="13:19">
@@ -8299,14 +8305,14 @@
         <v>17</v>
       </c>
       <c r="N141" t="s">
+        <v>509</v>
+      </c>
+      <c r="O141" t="s">
+        <v>234</v>
+      </c>
+      <c r="P141" t="s">
         <v>510</v>
       </c>
-      <c r="O141" t="s">
-        <v>235</v>
-      </c>
-      <c r="P141" t="s">
-        <v>511</v>
-      </c>
       <c r="Q141" t="s">
         <v>25</v>
       </c>
@@ -8314,7 +8320,7 @@
         <v>35</v>
       </c>
       <c r="S141" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="142" spans="13:19">
@@ -8322,14 +8328,14 @@
         <v>17</v>
       </c>
       <c r="N142" t="s">
+        <v>511</v>
+      </c>
+      <c r="O142" t="s">
+        <v>234</v>
+      </c>
+      <c r="P142" t="s">
         <v>512</v>
       </c>
-      <c r="O142" t="s">
-        <v>235</v>
-      </c>
-      <c r="P142" t="s">
-        <v>513</v>
-      </c>
       <c r="Q142" t="s">
         <v>25</v>
       </c>
@@ -8337,7 +8343,7 @@
         <v>35</v>
       </c>
       <c r="S142" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="143" spans="13:19">
@@ -8345,14 +8351,14 @@
         <v>17</v>
       </c>
       <c r="N143" t="s">
+        <v>513</v>
+      </c>
+      <c r="O143" t="s">
+        <v>234</v>
+      </c>
+      <c r="P143" t="s">
         <v>514</v>
       </c>
-      <c r="O143" t="s">
-        <v>235</v>
-      </c>
-      <c r="P143" t="s">
-        <v>515</v>
-      </c>
       <c r="Q143" t="s">
         <v>25</v>
       </c>
@@ -8360,7 +8366,7 @@
         <v>35</v>
       </c>
       <c r="S143" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="144" spans="13:19">
@@ -8368,14 +8374,14 @@
         <v>17</v>
       </c>
       <c r="N144" t="s">
+        <v>515</v>
+      </c>
+      <c r="O144" t="s">
+        <v>234</v>
+      </c>
+      <c r="P144" t="s">
         <v>516</v>
       </c>
-      <c r="O144" t="s">
-        <v>235</v>
-      </c>
-      <c r="P144" t="s">
-        <v>517</v>
-      </c>
       <c r="Q144" t="s">
         <v>25</v>
       </c>
@@ -8383,7 +8389,7 @@
         <v>35</v>
       </c>
       <c r="S144" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="145" spans="13:19">
@@ -8391,14 +8397,14 @@
         <v>17</v>
       </c>
       <c r="N145" t="s">
+        <v>517</v>
+      </c>
+      <c r="O145" t="s">
+        <v>234</v>
+      </c>
+      <c r="P145" t="s">
         <v>518</v>
       </c>
-      <c r="O145" t="s">
-        <v>235</v>
-      </c>
-      <c r="P145" t="s">
-        <v>519</v>
-      </c>
       <c r="Q145" t="s">
         <v>25</v>
       </c>
@@ -8406,7 +8412,7 @@
         <v>35</v>
       </c>
       <c r="S145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="146" spans="13:19">
@@ -8414,14 +8420,14 @@
         <v>17</v>
       </c>
       <c r="N146" t="s">
+        <v>519</v>
+      </c>
+      <c r="O146" t="s">
+        <v>234</v>
+      </c>
+      <c r="P146" t="s">
         <v>520</v>
       </c>
-      <c r="O146" t="s">
-        <v>235</v>
-      </c>
-      <c r="P146" t="s">
-        <v>521</v>
-      </c>
       <c r="Q146" t="s">
         <v>25</v>
       </c>
@@ -8429,7 +8435,7 @@
         <v>35</v>
       </c>
       <c r="S146" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="147" spans="13:19">
@@ -8437,14 +8443,14 @@
         <v>17</v>
       </c>
       <c r="N147" t="s">
+        <v>521</v>
+      </c>
+      <c r="O147" t="s">
+        <v>234</v>
+      </c>
+      <c r="P147" t="s">
         <v>522</v>
       </c>
-      <c r="O147" t="s">
-        <v>235</v>
-      </c>
-      <c r="P147" t="s">
-        <v>523</v>
-      </c>
       <c r="Q147" t="s">
         <v>25</v>
       </c>
@@ -8452,7 +8458,7 @@
         <v>35</v>
       </c>
       <c r="S147" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="148" spans="13:19">
@@ -8460,14 +8466,14 @@
         <v>17</v>
       </c>
       <c r="N148" t="s">
+        <v>523</v>
+      </c>
+      <c r="O148" t="s">
+        <v>234</v>
+      </c>
+      <c r="P148" t="s">
         <v>524</v>
       </c>
-      <c r="O148" t="s">
-        <v>235</v>
-      </c>
-      <c r="P148" t="s">
-        <v>525</v>
-      </c>
       <c r="Q148" t="s">
         <v>25</v>
       </c>
@@ -8475,7 +8481,7 @@
         <v>35</v>
       </c>
       <c r="S148" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="13:19">
@@ -8483,14 +8489,14 @@
         <v>17</v>
       </c>
       <c r="N149" t="s">
+        <v>525</v>
+      </c>
+      <c r="O149" t="s">
+        <v>234</v>
+      </c>
+      <c r="P149" t="s">
         <v>526</v>
       </c>
-      <c r="O149" t="s">
-        <v>235</v>
-      </c>
-      <c r="P149" t="s">
-        <v>527</v>
-      </c>
       <c r="Q149" t="s">
         <v>25</v>
       </c>
@@ -8498,7 +8504,7 @@
         <v>35</v>
       </c>
       <c r="S149" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="13:19">
@@ -8506,14 +8512,14 @@
         <v>17</v>
       </c>
       <c r="N150" t="s">
+        <v>527</v>
+      </c>
+      <c r="O150" t="s">
+        <v>234</v>
+      </c>
+      <c r="P150" t="s">
         <v>528</v>
       </c>
-      <c r="O150" t="s">
-        <v>235</v>
-      </c>
-      <c r="P150" t="s">
-        <v>529</v>
-      </c>
       <c r="Q150" t="s">
         <v>25</v>
       </c>
@@ -8521,7 +8527,7 @@
         <v>35</v>
       </c>
       <c r="S150" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="13:19">
@@ -8529,14 +8535,14 @@
         <v>17</v>
       </c>
       <c r="N151" t="s">
+        <v>529</v>
+      </c>
+      <c r="O151" t="s">
+        <v>234</v>
+      </c>
+      <c r="P151" t="s">
         <v>530</v>
       </c>
-      <c r="O151" t="s">
-        <v>235</v>
-      </c>
-      <c r="P151" t="s">
-        <v>531</v>
-      </c>
       <c r="Q151" t="s">
         <v>25</v>
       </c>
@@ -8544,7 +8550,7 @@
         <v>35</v>
       </c>
       <c r="S151" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="13:19">
@@ -8552,14 +8558,14 @@
         <v>17</v>
       </c>
       <c r="N152" t="s">
+        <v>531</v>
+      </c>
+      <c r="O152" t="s">
+        <v>234</v>
+      </c>
+      <c r="P152" t="s">
         <v>532</v>
       </c>
-      <c r="O152" t="s">
-        <v>235</v>
-      </c>
-      <c r="P152" t="s">
-        <v>533</v>
-      </c>
       <c r="Q152" t="s">
         <v>25</v>
       </c>
@@ -8567,7 +8573,7 @@
         <v>35</v>
       </c>
       <c r="S152" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="153" spans="13:19">
@@ -8575,14 +8581,14 @@
         <v>17</v>
       </c>
       <c r="N153" t="s">
+        <v>533</v>
+      </c>
+      <c r="O153" t="s">
+        <v>234</v>
+      </c>
+      <c r="P153" t="s">
         <v>534</v>
       </c>
-      <c r="O153" t="s">
-        <v>235</v>
-      </c>
-      <c r="P153" t="s">
-        <v>535</v>
-      </c>
       <c r="Q153" t="s">
         <v>25</v>
       </c>
@@ -8590,7 +8596,7 @@
         <v>35</v>
       </c>
       <c r="S153" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="154" spans="13:19">
@@ -8598,14 +8604,14 @@
         <v>17</v>
       </c>
       <c r="N154" t="s">
+        <v>535</v>
+      </c>
+      <c r="O154" t="s">
+        <v>234</v>
+      </c>
+      <c r="P154" t="s">
         <v>536</v>
       </c>
-      <c r="O154" t="s">
-        <v>235</v>
-      </c>
-      <c r="P154" t="s">
-        <v>537</v>
-      </c>
       <c r="Q154" t="s">
         <v>25</v>
       </c>
@@ -8613,7 +8619,7 @@
         <v>35</v>
       </c>
       <c r="S154" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="155" spans="13:19">
@@ -8621,14 +8627,14 @@
         <v>17</v>
       </c>
       <c r="N155" t="s">
+        <v>537</v>
+      </c>
+      <c r="O155" t="s">
+        <v>234</v>
+      </c>
+      <c r="P155" t="s">
         <v>538</v>
       </c>
-      <c r="O155" t="s">
-        <v>235</v>
-      </c>
-      <c r="P155" t="s">
-        <v>539</v>
-      </c>
       <c r="Q155" t="s">
         <v>25</v>
       </c>
@@ -8636,7 +8642,7 @@
         <v>35</v>
       </c>
       <c r="S155" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="156" spans="13:19">
@@ -8644,14 +8650,14 @@
         <v>17</v>
       </c>
       <c r="N156" t="s">
+        <v>539</v>
+      </c>
+      <c r="O156" t="s">
+        <v>234</v>
+      </c>
+      <c r="P156" t="s">
         <v>540</v>
       </c>
-      <c r="O156" t="s">
-        <v>235</v>
-      </c>
-      <c r="P156" t="s">
-        <v>541</v>
-      </c>
       <c r="Q156" t="s">
         <v>25</v>
       </c>
@@ -8659,7 +8665,7 @@
         <v>35</v>
       </c>
       <c r="S156" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="157" spans="13:19">
@@ -8667,14 +8673,14 @@
         <v>17</v>
       </c>
       <c r="N157" t="s">
+        <v>541</v>
+      </c>
+      <c r="O157" t="s">
+        <v>234</v>
+      </c>
+      <c r="P157" t="s">
         <v>542</v>
       </c>
-      <c r="O157" t="s">
-        <v>235</v>
-      </c>
-      <c r="P157" t="s">
-        <v>543</v>
-      </c>
       <c r="Q157" t="s">
         <v>25</v>
       </c>
@@ -8682,7 +8688,7 @@
         <v>35</v>
       </c>
       <c r="S157" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="158" spans="13:19">
@@ -8690,14 +8696,14 @@
         <v>17</v>
       </c>
       <c r="N158" t="s">
+        <v>543</v>
+      </c>
+      <c r="O158" t="s">
+        <v>234</v>
+      </c>
+      <c r="P158" t="s">
         <v>544</v>
       </c>
-      <c r="O158" t="s">
-        <v>235</v>
-      </c>
-      <c r="P158" t="s">
-        <v>545</v>
-      </c>
       <c r="Q158" t="s">
         <v>25</v>
       </c>
@@ -8705,7 +8711,7 @@
         <v>35</v>
       </c>
       <c r="S158" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="159" spans="13:19">
@@ -8713,14 +8719,14 @@
         <v>17</v>
       </c>
       <c r="N159" t="s">
+        <v>545</v>
+      </c>
+      <c r="O159" t="s">
+        <v>234</v>
+      </c>
+      <c r="P159" t="s">
         <v>546</v>
       </c>
-      <c r="O159" t="s">
-        <v>235</v>
-      </c>
-      <c r="P159" t="s">
-        <v>547</v>
-      </c>
       <c r="Q159" t="s">
         <v>25</v>
       </c>
@@ -8728,7 +8734,7 @@
         <v>35</v>
       </c>
       <c r="S159" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" spans="13:19">
@@ -8736,14 +8742,14 @@
         <v>17</v>
       </c>
       <c r="N160" t="s">
+        <v>547</v>
+      </c>
+      <c r="O160" t="s">
+        <v>234</v>
+      </c>
+      <c r="P160" t="s">
         <v>548</v>
       </c>
-      <c r="O160" t="s">
-        <v>235</v>
-      </c>
-      <c r="P160" t="s">
-        <v>549</v>
-      </c>
       <c r="Q160" t="s">
         <v>25</v>
       </c>
@@ -8751,7 +8757,7 @@
         <v>35</v>
       </c>
       <c r="S160" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="161" spans="13:19">
@@ -8759,14 +8765,14 @@
         <v>17</v>
       </c>
       <c r="N161" t="s">
+        <v>549</v>
+      </c>
+      <c r="O161" t="s">
+        <v>234</v>
+      </c>
+      <c r="P161" t="s">
         <v>550</v>
       </c>
-      <c r="O161" t="s">
-        <v>235</v>
-      </c>
-      <c r="P161" t="s">
-        <v>551</v>
-      </c>
       <c r="Q161" t="s">
         <v>25</v>
       </c>
@@ -8774,7 +8780,7 @@
         <v>35</v>
       </c>
       <c r="S161" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="162" spans="13:19">
@@ -8782,14 +8788,14 @@
         <v>17</v>
       </c>
       <c r="N162" t="s">
+        <v>551</v>
+      </c>
+      <c r="O162" t="s">
+        <v>234</v>
+      </c>
+      <c r="P162" t="s">
         <v>552</v>
       </c>
-      <c r="O162" t="s">
-        <v>235</v>
-      </c>
-      <c r="P162" t="s">
-        <v>553</v>
-      </c>
       <c r="Q162" t="s">
         <v>25</v>
       </c>
@@ -8797,7 +8803,7 @@
         <v>35</v>
       </c>
       <c r="S162" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="163" spans="13:19">
@@ -8805,14 +8811,14 @@
         <v>17</v>
       </c>
       <c r="N163" t="s">
+        <v>553</v>
+      </c>
+      <c r="O163" t="s">
+        <v>234</v>
+      </c>
+      <c r="P163" t="s">
         <v>554</v>
       </c>
-      <c r="O163" t="s">
-        <v>235</v>
-      </c>
-      <c r="P163" t="s">
-        <v>555</v>
-      </c>
       <c r="Q163" t="s">
         <v>25</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>35</v>
       </c>
       <c r="S163" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="164" spans="13:19">
@@ -8828,14 +8834,14 @@
         <v>17</v>
       </c>
       <c r="N164" t="s">
+        <v>555</v>
+      </c>
+      <c r="O164" t="s">
+        <v>234</v>
+      </c>
+      <c r="P164" t="s">
         <v>556</v>
       </c>
-      <c r="O164" t="s">
-        <v>235</v>
-      </c>
-      <c r="P164" t="s">
-        <v>557</v>
-      </c>
       <c r="Q164" t="s">
         <v>25</v>
       </c>
@@ -8843,7 +8849,7 @@
         <v>35</v>
       </c>
       <c r="S164" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="165" spans="13:19">
@@ -8851,14 +8857,14 @@
         <v>17</v>
       </c>
       <c r="N165" t="s">
+        <v>557</v>
+      </c>
+      <c r="O165" t="s">
+        <v>234</v>
+      </c>
+      <c r="P165" t="s">
         <v>558</v>
       </c>
-      <c r="O165" t="s">
-        <v>235</v>
-      </c>
-      <c r="P165" t="s">
-        <v>559</v>
-      </c>
       <c r="Q165" t="s">
         <v>25</v>
       </c>
@@ -8866,7 +8872,7 @@
         <v>35</v>
       </c>
       <c r="S165" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="166" spans="13:19">
@@ -8874,14 +8880,14 @@
         <v>17</v>
       </c>
       <c r="N166" t="s">
+        <v>559</v>
+      </c>
+      <c r="O166" t="s">
+        <v>234</v>
+      </c>
+      <c r="P166" t="s">
         <v>560</v>
       </c>
-      <c r="O166" t="s">
-        <v>235</v>
-      </c>
-      <c r="P166" t="s">
-        <v>561</v>
-      </c>
       <c r="Q166" t="s">
         <v>25</v>
       </c>
@@ -8889,7 +8895,7 @@
         <v>35</v>
       </c>
       <c r="S166" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="13:19">
@@ -8897,14 +8903,14 @@
         <v>17</v>
       </c>
       <c r="N167" t="s">
+        <v>561</v>
+      </c>
+      <c r="O167" t="s">
+        <v>234</v>
+      </c>
+      <c r="P167" t="s">
         <v>562</v>
       </c>
-      <c r="O167" t="s">
-        <v>235</v>
-      </c>
-      <c r="P167" t="s">
-        <v>563</v>
-      </c>
       <c r="Q167" t="s">
         <v>25</v>
       </c>
@@ -8912,7 +8918,7 @@
         <v>35</v>
       </c>
       <c r="S167" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="168" spans="13:19">
@@ -8920,14 +8926,14 @@
         <v>17</v>
       </c>
       <c r="N168" t="s">
+        <v>563</v>
+      </c>
+      <c r="O168" t="s">
+        <v>234</v>
+      </c>
+      <c r="P168" t="s">
         <v>564</v>
       </c>
-      <c r="O168" t="s">
-        <v>235</v>
-      </c>
-      <c r="P168" t="s">
-        <v>565</v>
-      </c>
       <c r="Q168" t="s">
         <v>25</v>
       </c>
@@ -8935,7 +8941,7 @@
         <v>35</v>
       </c>
       <c r="S168" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169" spans="13:19">
@@ -8943,14 +8949,14 @@
         <v>17</v>
       </c>
       <c r="N169" t="s">
+        <v>565</v>
+      </c>
+      <c r="O169" t="s">
+        <v>234</v>
+      </c>
+      <c r="P169" t="s">
         <v>566</v>
       </c>
-      <c r="O169" t="s">
-        <v>235</v>
-      </c>
-      <c r="P169" t="s">
-        <v>567</v>
-      </c>
       <c r="Q169" t="s">
         <v>25</v>
       </c>
@@ -8958,7 +8964,7 @@
         <v>35</v>
       </c>
       <c r="S169" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="170" spans="13:19">
@@ -8966,14 +8972,14 @@
         <v>17</v>
       </c>
       <c r="N170" t="s">
+        <v>567</v>
+      </c>
+      <c r="O170" t="s">
+        <v>234</v>
+      </c>
+      <c r="P170" t="s">
         <v>568</v>
       </c>
-      <c r="O170" t="s">
-        <v>235</v>
-      </c>
-      <c r="P170" t="s">
-        <v>569</v>
-      </c>
       <c r="Q170" t="s">
         <v>25</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>35</v>
       </c>
       <c r="S170" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171" spans="13:19">
@@ -8989,14 +8995,14 @@
         <v>17</v>
       </c>
       <c r="N171" t="s">
+        <v>569</v>
+      </c>
+      <c r="O171" t="s">
+        <v>234</v>
+      </c>
+      <c r="P171" t="s">
         <v>570</v>
       </c>
-      <c r="O171" t="s">
-        <v>235</v>
-      </c>
-      <c r="P171" t="s">
-        <v>571</v>
-      </c>
       <c r="Q171" t="s">
         <v>25</v>
       </c>
@@ -9004,7 +9010,7 @@
         <v>35</v>
       </c>
       <c r="S171" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="172" spans="13:19">
@@ -9012,14 +9018,14 @@
         <v>17</v>
       </c>
       <c r="N172" t="s">
+        <v>571</v>
+      </c>
+      <c r="O172" t="s">
+        <v>234</v>
+      </c>
+      <c r="P172" t="s">
         <v>572</v>
       </c>
-      <c r="O172" t="s">
-        <v>235</v>
-      </c>
-      <c r="P172" t="s">
-        <v>573</v>
-      </c>
       <c r="Q172" t="s">
         <v>25</v>
       </c>
@@ -9027,7 +9033,7 @@
         <v>35</v>
       </c>
       <c r="S172" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="173" spans="13:19">
@@ -9035,14 +9041,14 @@
         <v>17</v>
       </c>
       <c r="N173" t="s">
+        <v>573</v>
+      </c>
+      <c r="O173" t="s">
+        <v>234</v>
+      </c>
+      <c r="P173" t="s">
         <v>574</v>
       </c>
-      <c r="O173" t="s">
-        <v>235</v>
-      </c>
-      <c r="P173" t="s">
-        <v>575</v>
-      </c>
       <c r="Q173" t="s">
         <v>25</v>
       </c>
@@ -9050,7 +9056,7 @@
         <v>35</v>
       </c>
       <c r="S173" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -9463,7 +9469,7 @@
     </row>
     <row r="9" spans="2:12">
       <c r="D9" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E9" s="11">
         <v>0</v>
@@ -9474,7 +9480,7 @@
     </row>
     <row r="10" spans="2:12">
       <c r="D10" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10" s="11">
         <v>0</v>
@@ -9485,7 +9491,7 @@
     </row>
     <row r="11" spans="2:12">
       <c r="D11" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E11" s="11">
         <v>0</v>
@@ -9547,16 +9553,21 @@
         <v>8888</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>68</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="D18" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="F18" s="11">
+        <v>8888</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>611</v>
+      </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
@@ -9944,13 +9955,13 @@
     <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -9958,7 +9969,7 @@
     <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>49</v>
@@ -9967,10 +9978,10 @@
         <v>51</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I3" s="4">
         <v>2022</v>
@@ -9979,23 +9990,23 @@
         <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I4" s="11">
         <v>0.05</v>
@@ -10004,10 +10015,10 @@
         <v>25</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="N4" s="6">
         <v>1055.55</v>
@@ -10016,13 +10027,13 @@
     <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>187</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
@@ -10031,10 +10042,10 @@
         <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="6">
         <v>3.6</v>
@@ -10043,19 +10054,19 @@
     <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I6" s="11">
         <v>2025</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="N6" s="6">
         <v>1000</v>
@@ -10064,19 +10075,19 @@
     <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" s="11">
         <v>1</v>
       </c>
       <c r="L7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="N7" s="6">
         <v>1000</v>
@@ -10085,25 +10096,25 @@
     <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="11">
         <v>2.2201</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" s="6">
         <v>1.05555</v>
@@ -10112,25 +10123,25 @@
     <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" s="11">
         <v>2.1427</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="6">
         <v>4.1868000000000002E-2</v>
@@ -10139,25 +10150,25 @@
     <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I10" s="11">
         <v>2.077</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N10" s="6">
         <v>41.868000000000002</v>
@@ -10166,25 +10177,25 @@
     <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I11" s="11">
         <v>2.0358000000000001</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N11" s="6">
         <v>3.5999999999999999E-3</v>
@@ -10193,25 +10204,25 @@
     <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I12" s="11">
         <v>1.9870000000000001</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N12" s="6">
         <v>1000000</v>
@@ -10220,25 +10231,25 @@
     <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I13" s="11">
         <v>1.9192</v>
       </c>
       <c r="L13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="N13" s="6">
         <v>1000</v>
@@ -10247,25 +10258,25 @@
     <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I14" s="11">
         <v>1.8468</v>
       </c>
       <c r="L14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="N14" s="6">
         <v>5.8615199999999996</v>
@@ -10274,25 +10285,25 @@
     <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I15" s="11">
         <v>1.7799</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="N15" s="6">
         <v>1E-3</v>
@@ -10301,25 +10312,25 @@
     <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="11">
         <v>1.722</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N16" s="6">
         <v>1000</v>
@@ -10328,25 +10339,25 @@
     <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" s="11">
         <v>1.6836</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N17" s="6">
         <v>37.68</v>
@@ -10354,25 +10365,25 @@
     </row>
     <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I18" s="11">
         <v>1.6446000000000001</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N18" s="6">
         <v>2139.4548</v>
@@ -10380,25 +10391,25 @@
     </row>
     <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="11">
         <v>1.6102000000000001</v>
       </c>
       <c r="L19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="N19" s="6">
         <v>2.78</v>
@@ -10406,25 +10417,25 @@
     </row>
     <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I20" s="11">
         <v>1.5770999999999999</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N20" s="6">
         <v>3.6</v>
@@ -10432,25 +10443,25 @@
     </row>
     <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I21" s="11">
         <v>1.5488</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -10458,25 +10469,25 @@
     </row>
     <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" s="11">
         <v>1.5224</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N22" s="6">
         <v>31.536000000000001</v>
@@ -10484,25 +10495,25 @@
     </row>
     <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I23" s="11">
         <v>1.5058</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N23" s="6">
         <v>120</v>
@@ -10510,25 +10521,25 @@
     </row>
     <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I24" s="11">
         <v>1.4844999999999999</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N24" s="11">
         <v>5.8615199999999996</v>
@@ -10536,25 +10547,25 @@
     </row>
     <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I25" s="11">
         <v>1.4518</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N25" s="11">
         <v>54</v>
@@ -10562,16 +10573,16 @@
     </row>
     <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="11">
         <v>1.4198999999999999</v>
@@ -10579,16 +10590,16 @@
     </row>
     <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" s="11">
         <v>1.3986000000000001</v>
@@ -10596,16 +10607,16 @@
     </row>
     <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="11">
         <v>1.3727</v>
@@ -10613,16 +10624,16 @@
     </row>
     <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I29" s="11">
         <v>1.3369</v>
@@ -10630,16 +10641,16 @@
     </row>
     <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I30" s="11">
         <v>1.2967</v>
@@ -10647,16 +10658,16 @@
     </row>
     <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I31" s="11">
         <v>1.2583</v>
@@ -10664,16 +10675,16 @@
     </row>
     <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I32" s="11">
         <v>1.2253000000000001</v>
@@ -10681,16 +10692,16 @@
     </row>
     <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I33" s="11">
         <v>1.2023999999999999</v>
@@ -10698,16 +10709,16 @@
     </row>
     <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I34" s="11">
         <v>1.1931</v>
@@ -10715,16 +10726,16 @@
     </row>
     <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I35" s="11">
         <v>1.1793</v>
@@ -10732,16 +10743,16 @@
     </row>
     <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I36" s="11">
         <v>1.1552</v>
@@ -10749,16 +10760,16 @@
     </row>
     <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I37" s="11">
         <v>1.1334</v>
@@ -10766,16 +10777,16 @@
     </row>
     <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I38" s="11">
         <v>1.1136999999999999</v>
@@ -10783,16 +10794,16 @@
     </row>
     <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39" s="11">
         <v>1.0934999999999999</v>
@@ -10800,16 +10811,16 @@
     </row>
     <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I40" s="11">
         <v>1.0831</v>
@@ -10817,16 +10828,16 @@
     </row>
     <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I41" s="11">
         <v>1.0719000000000001</v>
@@ -10834,16 +10845,16 @@
     </row>
     <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I42" s="11">
         <v>1.0519000000000001</v>
@@ -10851,16 +10862,16 @@
     </row>
     <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I43" s="11">
         <v>1.0274000000000001</v>
@@ -10868,16 +10879,16 @@
     </row>
     <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I44" s="11">
         <v>1.0091000000000001</v>
@@ -10885,16 +10896,16 @@
     </row>
     <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I45" s="11">
         <v>1</v>
@@ -10902,16 +10913,16 @@
     </row>
     <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I46" s="11">
         <v>0.98960000000000004</v>
@@ -10919,16 +10930,16 @@
     </row>
     <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I47" s="11">
         <v>0.97809999999999997</v>
@@ -10936,16 +10947,16 @@
     </row>
     <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I48" s="11">
         <v>0.96499999999999997</v>
@@ -10953,16 +10964,16 @@
     </row>
     <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I49" s="11">
         <v>0.94910000000000005</v>
@@ -10970,16 +10981,16 @@
     </row>
     <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I50" s="11">
         <v>0.92969999999999997</v>
@@ -10987,7 +10998,7 @@
     </row>
     <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>F46</f>
@@ -10998,7 +11009,7 @@
         <v>USD20</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I51" s="11">
         <f t="shared" si="0"/>
@@ -11007,13 +11018,13 @@
     </row>
     <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I52" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11021,13 +11032,13 @@
     </row>
     <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I53" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11035,13 +11046,13 @@
     </row>
     <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I54" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11049,10 +11060,10 @@
     </row>
     <row r="55" spans="2:9">
       <c r="F55" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I55" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11060,10 +11071,10 @@
     </row>
     <row r="56" spans="2:9">
       <c r="F56" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I56" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11071,10 +11082,10 @@
     </row>
     <row r="57" spans="2:9">
       <c r="F57" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I57" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11082,10 +11093,10 @@
     </row>
     <row r="58" spans="2:9">
       <c r="F58" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I58" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11093,10 +11104,10 @@
     </row>
     <row r="59" spans="2:9">
       <c r="F59" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I59" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11104,10 +11115,10 @@
     </row>
     <row r="60" spans="2:9">
       <c r="F60" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I60" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11115,10 +11126,10 @@
     </row>
     <row r="61" spans="2:9">
       <c r="F61" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I61" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11126,10 +11137,10 @@
     </row>
     <row r="62" spans="2:9">
       <c r="F62" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I62" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11137,10 +11148,10 @@
     </row>
     <row r="63" spans="2:9">
       <c r="F63" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I63" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11148,10 +11159,10 @@
     </row>
     <row r="64" spans="2:9">
       <c r="F64" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I64" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11159,10 +11170,10 @@
     </row>
     <row r="65" spans="6:9">
       <c r="F65" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I65" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11170,10 +11181,10 @@
     </row>
     <row r="66" spans="6:9">
       <c r="F66" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I66" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11181,10 +11192,10 @@
     </row>
     <row r="67" spans="6:9">
       <c r="F67" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I67" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11192,10 +11203,10 @@
     </row>
     <row r="68" spans="6:9">
       <c r="F68" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I68" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11203,10 +11214,10 @@
     </row>
     <row r="69" spans="6:9">
       <c r="F69" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I69" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11214,10 +11225,10 @@
     </row>
     <row r="70" spans="6:9">
       <c r="F70" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I70" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11225,10 +11236,10 @@
     </row>
     <row r="71" spans="6:9">
       <c r="F71" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I71" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11236,10 +11247,10 @@
     </row>
     <row r="72" spans="6:9">
       <c r="F72" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I72" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11247,10 +11258,10 @@
     </row>
     <row r="73" spans="6:9">
       <c r="F73" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I73" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11258,10 +11269,10 @@
     </row>
     <row r="74" spans="6:9">
       <c r="F74" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I74" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11269,10 +11280,10 @@
     </row>
     <row r="75" spans="6:9">
       <c r="F75" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I75" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11280,10 +11291,10 @@
     </row>
     <row r="76" spans="6:9">
       <c r="F76" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I76" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11291,10 +11302,10 @@
     </row>
     <row r="77" spans="6:9">
       <c r="F77" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I77" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11302,10 +11313,10 @@
     </row>
     <row r="78" spans="6:9">
       <c r="F78" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I78" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11313,10 +11324,10 @@
     </row>
     <row r="79" spans="6:9">
       <c r="F79" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I79" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11324,10 +11335,10 @@
     </row>
     <row r="80" spans="6:9">
       <c r="F80" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I80" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11335,10 +11346,10 @@
     </row>
     <row r="81" spans="6:9">
       <c r="F81" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I81" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11346,10 +11357,10 @@
     </row>
     <row r="82" spans="6:9">
       <c r="F82" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I82" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11357,10 +11368,10 @@
     </row>
     <row r="83" spans="6:9">
       <c r="F83" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I83" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11368,10 +11379,10 @@
     </row>
     <row r="84" spans="6:9">
       <c r="F84" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I84" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11379,10 +11390,10 @@
     </row>
     <row r="85" spans="6:9">
       <c r="F85" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I85" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11390,10 +11401,10 @@
     </row>
     <row r="86" spans="6:9">
       <c r="F86" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I86" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11401,10 +11412,10 @@
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I87" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11412,10 +11423,10 @@
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I88" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11423,10 +11434,10 @@
     </row>
     <row r="89" spans="6:9">
       <c r="F89" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I89" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11434,10 +11445,10 @@
     </row>
     <row r="90" spans="6:9">
       <c r="F90" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I90" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11445,10 +11456,10 @@
     </row>
     <row r="91" spans="6:9">
       <c r="F91" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I91" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11456,10 +11467,10 @@
     </row>
     <row r="92" spans="6:9">
       <c r="F92" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I92" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11467,10 +11478,10 @@
     </row>
     <row r="93" spans="6:9">
       <c r="F93" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I93" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11478,10 +11489,10 @@
     </row>
     <row r="94" spans="6:9">
       <c r="F94" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I94" s="11">
         <v>7.0000000000000007E-2</v>
@@ -11489,7 +11500,7 @@
     </row>
     <row r="95" spans="6:9">
       <c r="F95" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H95" s="11" t="str">
         <f>H51</f>
@@ -11501,7 +11512,7 @@
     </row>
     <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
       <c r="E99" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
@@ -11512,10 +11523,10 @@
         <v>51</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I100" s="4">
         <v>2022</v>
@@ -11527,13 +11538,13 @@
     <row r="101" spans="5:10" ht="14.25">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H101" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I101" s="22">
         <f>1.10926234054354*I40</f>
@@ -11543,11 +11554,11 @@
     <row r="102" spans="5:10" ht="14.25">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G102"/>
       <c r="H102" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I102" s="22">
         <f>I84</f>
@@ -11580,7 +11591,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>53</v>
@@ -11588,10 +11599,10 @@
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="D5" s="6">
         <v>-1</v>
@@ -11599,10 +11610,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -11610,10 +11621,10 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -11621,10 +11632,10 @@
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -11632,10 +11643,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -11643,10 +11654,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -11654,10 +11665,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -11665,10 +11676,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -11676,10 +11687,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -11687,10 +11698,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -11698,10 +11709,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -11709,10 +11720,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D16" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11720,10 +11731,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11731,10 +11742,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D18" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11742,10 +11753,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D19" s="16">
         <v>1.0000000000000001E-5</v>
@@ -11753,10 +11764,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="D20" s="17">
         <v>1</v>
@@ -11764,73 +11775,73 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B25" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98F9878-5608-48D1-8294-3B3CCB93FAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34FBD5C-B2A5-4051-A589-152C7478B5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="613">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1875,6 +1875,9 @@
   </si>
   <si>
     <t>IMPDUCZ</t>
+  </si>
+  <si>
+    <t>peakts</t>
   </si>
 </sst>
 </file>
@@ -4290,15 +4293,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D623F0-8ADB-4F5C-B508-FD1AC14986D0}">
-  <dimension ref="B3:I20"/>
+  <dimension ref="B3:J20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="10" max="10" width="6.06640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>218</v>
       </c>
@@ -4323,8 +4329,11 @@
       <c r="I4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="2:9">
+      <c r="J4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -4349,8 +4358,11 @@
       <c r="I5" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="6" spans="2:9">
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>17</v>
       </c>
@@ -4375,8 +4387,11 @@
       <c r="I6" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="7" spans="2:9">
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -4401,8 +4416,11 @@
       <c r="I7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="8" spans="2:9">
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -4427,8 +4445,11 @@
       <c r="I8" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="9" spans="2:9">
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -4453,8 +4474,11 @@
       <c r="I9" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="10" spans="2:9">
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -4479,8 +4503,11 @@
       <c r="I10" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="11" spans="2:9">
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -4505,8 +4532,11 @@
       <c r="I11" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="12" spans="2:9">
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -4531,8 +4561,11 @@
       <c r="I12" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="13" spans="2:9">
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
         <v>17</v>
       </c>
@@ -4557,8 +4590,11 @@
       <c r="I13" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="14" spans="2:9">
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
       <c r="B14" t="s">
         <v>17</v>
       </c>
@@ -4583,8 +4619,11 @@
       <c r="I14" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="15" spans="2:9">
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="B15" t="s">
         <v>17</v>
       </c>
@@ -4609,8 +4648,11 @@
       <c r="I15" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="16" spans="2:9">
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -4635,8 +4677,11 @@
       <c r="I16" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -4661,8 +4706,11 @@
       <c r="I17" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="18" spans="2:9">
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>17</v>
       </c>
@@ -4687,8 +4735,11 @@
       <c r="I18" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>17</v>
       </c>
@@ -4713,8 +4764,11 @@
       <c r="I19" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="20" spans="2:9">
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" t="s">
         <v>17</v>
       </c>
@@ -4738,6 +4792,9 @@
       </c>
       <c r="I20" t="s">
         <v>238</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34FBD5C-B2A5-4051-A589-152C7478B5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD99D9-BE6C-482F-950D-3105877D5735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -10066,10 +10066,10 @@
         <v>184</v>
       </c>
       <c r="I4" s="11">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>83</v>
